--- a/Paper/_output/_comparison/compare_all.xlsx
+++ b/Paper/_output/_comparison/compare_all.xlsx
@@ -8,13 +8,14 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="overall" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dotcom" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GFC" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2018 Q4" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Covid" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2022 rates" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025 tariffs" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="windows" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="vs_base" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dotcom" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GFC" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2018 Q4" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Covid" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2022 rates" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025 tariffs" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="windows" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -11039,6 +11040,9765 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:AC94"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="21" customWidth="1" min="15" max="15"/>
+    <col width="24" customWidth="1" min="16" max="16"/>
+    <col width="22" customWidth="1" min="17" max="17"/>
+    <col width="11" customWidth="1" min="18" max="18"/>
+    <col width="21" customWidth="1" min="19" max="19"/>
+    <col width="24" customWidth="1" min="20" max="20"/>
+    <col width="21" customWidth="1" min="21" max="21"/>
+    <col width="25" customWidth="1" min="22" max="22"/>
+    <col width="22" customWidth="1" min="23" max="23"/>
+    <col width="24" customWidth="1" min="24" max="24"/>
+    <col width="22" customWidth="1" min="25" max="25"/>
+    <col width="23" customWidth="1" min="26" max="26"/>
+    <col width="22" customWidth="1" min="27" max="27"/>
+    <col width="23" customWidth="1" min="28" max="28"/>
+    <col width="22" customWidth="1" min="29" max="29"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>frequency</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>detector</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>series</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>crisis_target</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>d_sharpe</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>p_sharpe</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>d_ann_return</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>p_ann_return</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>d_ann_vol</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>p_ann_vol</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>d_cum_return</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>p_cum_return</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>d_max_dd</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>p_max_dd</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>d_dd_days</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>p_dd_days</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>d_calmar</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>p_calmar</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>d_ulcer</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>p_ulcer</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>d_var_95</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>p_var_95</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>d_cvar_95</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>p_cvar_95</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>d_beta</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>p_beta</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>mvo</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>always min_var</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>mvo_t_10_lw_minvar</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>mvo_t_10_lw</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="n">
+        <v>0.01118514642038742</v>
+      </c>
+      <c r="I2" s="4" t="n">
+        <v>0.8900016387568849</v>
+      </c>
+      <c r="J2" s="3" t="n">
+        <v>-0.00993546370150189</v>
+      </c>
+      <c r="K2" s="4" t="n">
+        <v>0.5614385614385614</v>
+      </c>
+      <c r="L2" s="3" t="n">
+        <v>-0.02901526212510067</v>
+      </c>
+      <c r="M2" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="N2" s="3" t="n">
+        <v>-3.088573984664126</v>
+      </c>
+      <c r="O2" s="4" t="n">
+        <v>0.6313686313686314</v>
+      </c>
+      <c r="P2" s="3" t="n">
+        <v>0.1661103411223522</v>
+      </c>
+      <c r="Q2" s="4" t="n">
+        <v>0.06593406593406594</v>
+      </c>
+      <c r="R2" s="2" t="n">
+        <v>-2128</v>
+      </c>
+      <c r="S2" s="4" t="n">
+        <v>0.3436563436563437</v>
+      </c>
+      <c r="T2" s="4" t="n">
+        <v>0.05421090158021855</v>
+      </c>
+      <c r="U2" s="4" t="n">
+        <v>0.4425574425574426</v>
+      </c>
+      <c r="V2" s="4" t="n">
+        <v>-0.116971742438072</v>
+      </c>
+      <c r="W2" s="4" t="n">
+        <v>0.04395604395604396</v>
+      </c>
+      <c r="X2" s="3" t="n">
+        <v>0.003629406349018614</v>
+      </c>
+      <c r="Y2" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="Z2" s="3" t="n">
+        <v>0.00446439355283209</v>
+      </c>
+      <c r="AA2" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="AB2" s="4" t="n">
+        <v>-0.1889635245287776</v>
+      </c>
+      <c r="AC2" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>mvo</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>mvo_t_10_lw_changepoint_vix_cash</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>mvo_t_10_lw</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="n">
+        <v>-0.1760927117869723</v>
+      </c>
+      <c r="I3" s="4" t="n">
+        <v>0.2131622906446128</v>
+      </c>
+      <c r="J3" s="3" t="n">
+        <v>-0.05120018873225227</v>
+      </c>
+      <c r="K3" s="4" t="n">
+        <v>0.05194805194805195</v>
+      </c>
+      <c r="L3" s="3" t="n">
+        <v>-0.0680965994675779</v>
+      </c>
+      <c r="M3" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>-10.14476813068077</v>
+      </c>
+      <c r="O3" s="4" t="n">
+        <v>0.2727272727272727</v>
+      </c>
+      <c r="P3" s="3" t="n">
+        <v>0.1273901532733914</v>
+      </c>
+      <c r="Q3" s="4" t="n">
+        <v>0.2457542457542458</v>
+      </c>
+      <c r="R3" s="2" t="n">
+        <v>-1585</v>
+      </c>
+      <c r="S3" s="4" t="n">
+        <v>0.6863136863136863</v>
+      </c>
+      <c r="T3" s="4" t="n">
+        <v>-0.06779324459340001</v>
+      </c>
+      <c r="U3" s="4" t="n">
+        <v>0.5414585414585414</v>
+      </c>
+      <c r="V3" s="4" t="n">
+        <v>-0.07175118436211692</v>
+      </c>
+      <c r="W3" s="4" t="n">
+        <v>0.3936063936063936</v>
+      </c>
+      <c r="X3" s="3" t="n">
+        <v>0.008142073340493371</v>
+      </c>
+      <c r="Y3" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="Z3" s="3" t="n">
+        <v>0.008570588359284637</v>
+      </c>
+      <c r="AA3" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="AB3" s="4" t="n">
+        <v>-0.5443587927520298</v>
+      </c>
+      <c r="AC3" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>mvo</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>hmm</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>gspc</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>mvo_t_10_lw_hmm_gspc_cash</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>mvo_t_10_lw</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="n">
+        <v>-0.03999033900869315</v>
+      </c>
+      <c r="I4" s="4" t="n">
+        <v>0.7453099543750883</v>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>-0.02670586631277616</v>
+      </c>
+      <c r="K4" s="4" t="n">
+        <v>0.1498501498501499</v>
+      </c>
+      <c r="L4" s="3" t="n">
+        <v>-0.05012623124170565</v>
+      </c>
+      <c r="M4" s="4" t="n">
+        <v>0.001998001998001998</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>-6.849825671577779</v>
+      </c>
+      <c r="O4" s="4" t="n">
+        <v>0.3346653346653347</v>
+      </c>
+      <c r="P4" s="3" t="n">
+        <v>-0.06928969640913607</v>
+      </c>
+      <c r="Q4" s="4" t="n">
+        <v>0.6943056943056943</v>
+      </c>
+      <c r="R4" s="2" t="n">
+        <v>405</v>
+      </c>
+      <c r="S4" s="4" t="n">
+        <v>0.5104895104895105</v>
+      </c>
+      <c r="T4" s="4" t="n">
+        <v>-0.06446921075672414</v>
+      </c>
+      <c r="U4" s="4" t="n">
+        <v>0.4175824175824176</v>
+      </c>
+      <c r="V4" s="4" t="n">
+        <v>0.06624337909303271</v>
+      </c>
+      <c r="W4" s="4" t="n">
+        <v>0.5254745254745254</v>
+      </c>
+      <c r="X4" s="3" t="n">
+        <v>0.004315890415394069</v>
+      </c>
+      <c r="Y4" s="4" t="n">
+        <v>0.002997002997002997</v>
+      </c>
+      <c r="Z4" s="3" t="n">
+        <v>0.006344042596393495</v>
+      </c>
+      <c r="AA4" s="4" t="n">
+        <v>0.006993006993006993</v>
+      </c>
+      <c r="AB4" s="4" t="n">
+        <v>-0.4300692654676035</v>
+      </c>
+      <c r="AC4" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>mvo</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>mvo_t_10_lw_wasserstein_gspc_vix_cash</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>mvo_t_10_lw</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="n">
+        <v>0.0381701648689093</v>
+      </c>
+      <c r="I5" s="4" t="n">
+        <v>0.8134505849857016</v>
+      </c>
+      <c r="J5" s="3" t="n">
+        <v>-0.03070938436131172</v>
+      </c>
+      <c r="K5" s="4" t="n">
+        <v>0.1938061938061938</v>
+      </c>
+      <c r="L5" s="3" t="n">
+        <v>-0.08616713406286169</v>
+      </c>
+      <c r="M5" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="N5" s="3" t="n">
+        <v>-7.53734372494384</v>
+      </c>
+      <c r="O5" s="4" t="n">
+        <v>0.3746253746253747</v>
+      </c>
+      <c r="P5" s="3" t="n">
+        <v>0.3315620882419186</v>
+      </c>
+      <c r="Q5" s="4" t="n">
+        <v>0.01998001998001998</v>
+      </c>
+      <c r="R5" s="2" t="n">
+        <v>-1716</v>
+      </c>
+      <c r="S5" s="4" t="n">
+        <v>0.4305694305694306</v>
+      </c>
+      <c r="T5" s="4" t="n">
+        <v>0.1418159763027955</v>
+      </c>
+      <c r="U5" s="4" t="n">
+        <v>0.3446553446553446</v>
+      </c>
+      <c r="V5" s="4" t="n">
+        <v>-0.1201320000396721</v>
+      </c>
+      <c r="W5" s="4" t="n">
+        <v>0.06893106893106893</v>
+      </c>
+      <c r="X5" s="3" t="n">
+        <v>0.008307420384208829</v>
+      </c>
+      <c r="Y5" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="Z5" s="3" t="n">
+        <v>0.01141487240595076</v>
+      </c>
+      <c r="AA5" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="AB5" s="4" t="n">
+        <v>-0.6429479290235276</v>
+      </c>
+      <c r="AC5" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>mvo</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>min_var</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>mvo_t_10_lw_changepoint_vix_min_var</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>mvo_t_10_lw</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="n">
+        <v>0.01944067647000738</v>
+      </c>
+      <c r="I6" s="4" t="n">
+        <v>0.743586405534123</v>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>-0.002669266327450334</v>
+      </c>
+      <c r="K6" s="4" t="n">
+        <v>0.8211788211788211</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>-0.01564516175389116</v>
+      </c>
+      <c r="M6" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>-0.9053354007850754</v>
+      </c>
+      <c r="O6" s="4" t="n">
+        <v>0.8191808191808192</v>
+      </c>
+      <c r="P6" s="3" t="n">
+        <v>0.1025826970718816</v>
+      </c>
+      <c r="Q6" s="4" t="n">
+        <v>0.09090909090909091</v>
+      </c>
+      <c r="R6" s="2" t="n">
+        <v>-1368</v>
+      </c>
+      <c r="S6" s="4" t="n">
+        <v>0.3406593406593407</v>
+      </c>
+      <c r="T6" s="4" t="n">
+        <v>0.03653688660697019</v>
+      </c>
+      <c r="U6" s="4" t="n">
+        <v>0.3926073926073926</v>
+      </c>
+      <c r="V6" s="4" t="n">
+        <v>-0.0722224493625358</v>
+      </c>
+      <c r="W6" s="4" t="n">
+        <v>0.06393606393606394</v>
+      </c>
+      <c r="X6" s="3" t="n">
+        <v>0.002476554762338268</v>
+      </c>
+      <c r="Y6" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="Z6" s="3" t="n">
+        <v>0.002294220323144983</v>
+      </c>
+      <c r="AA6" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="AB6" s="4" t="n">
+        <v>-0.1031791599832037</v>
+      </c>
+      <c r="AC6" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>mvo</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>hmm</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>gspc</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>min_var</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>mvo_t_10_lw_hmm_gspc_min_var</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>mvo_t_10_lw</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="n">
+        <v>0.03665627728369857</v>
+      </c>
+      <c r="I7" s="4" t="n">
+        <v>0.3533075527389913</v>
+      </c>
+      <c r="J7" s="3" t="n">
+        <v>0.0028628550300515</v>
+      </c>
+      <c r="K7" s="4" t="n">
+        <v>0.6643356643356644</v>
+      </c>
+      <c r="L7" s="3" t="n">
+        <v>-0.01086696520323635</v>
+      </c>
+      <c r="M7" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>1.039189511740123</v>
+      </c>
+      <c r="O7" s="4" t="n">
+        <v>0.6353646353646354</v>
+      </c>
+      <c r="P7" s="3" t="n">
+        <v>-0.01376216217756776</v>
+      </c>
+      <c r="Q7" s="4" t="n">
+        <v>0.8901098901098901</v>
+      </c>
+      <c r="R7" s="2" t="n">
+        <v>-223</v>
+      </c>
+      <c r="S7" s="4" t="n">
+        <v>0.4595404595404595</v>
+      </c>
+      <c r="T7" s="4" t="n">
+        <v>0.0006454380578965191</v>
+      </c>
+      <c r="U7" s="4" t="n">
+        <v>0.984015984015984</v>
+      </c>
+      <c r="V7" s="4" t="n">
+        <v>0.001005855796471306</v>
+      </c>
+      <c r="W7" s="4" t="n">
+        <v>0.971028971028971</v>
+      </c>
+      <c r="X7" s="3" t="n">
+        <v>0.001249523182465909</v>
+      </c>
+      <c r="Y7" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="Z7" s="3" t="n">
+        <v>0.00168697524327922</v>
+      </c>
+      <c r="AA7" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="AB7" s="4" t="n">
+        <v>-0.06950929532032546</v>
+      </c>
+      <c r="AC7" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>mvo</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>min_var</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>mvo_t_10_lw_wasserstein_gspc_vix_min_var</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>mvo_t_10_lw</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="n">
+        <v>0.05813793628601097</v>
+      </c>
+      <c r="I8" s="4" t="n">
+        <v>0.3288618710522819</v>
+      </c>
+      <c r="J8" s="3" t="n">
+        <v>0.003382047305880223</v>
+      </c>
+      <c r="K8" s="4" t="n">
+        <v>0.7462537462537463</v>
+      </c>
+      <c r="L8" s="3" t="n">
+        <v>-0.01880891354459735</v>
+      </c>
+      <c r="M8" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>1.235579255504261</v>
+      </c>
+      <c r="O8" s="4" t="n">
+        <v>0.6813186813186813</v>
+      </c>
+      <c r="P8" s="3" t="n">
+        <v>0.07346448455825483</v>
+      </c>
+      <c r="Q8" s="4" t="n">
+        <v>0.07492507492507493</v>
+      </c>
+      <c r="R8" s="2" t="n">
+        <v>-1150</v>
+      </c>
+      <c r="S8" s="4" t="n">
+        <v>0.2647352647352647</v>
+      </c>
+      <c r="T8" s="4" t="n">
+        <v>0.03586722277974405</v>
+      </c>
+      <c r="U8" s="4" t="n">
+        <v>0.3336663336663337</v>
+      </c>
+      <c r="V8" s="4" t="n">
+        <v>-0.05966782480076047</v>
+      </c>
+      <c r="W8" s="4" t="n">
+        <v>0.03796203796203796</v>
+      </c>
+      <c r="X8" s="3" t="n">
+        <v>0.002588535960227258</v>
+      </c>
+      <c r="Y8" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="Z8" s="3" t="n">
+        <v>0.002929843827322857</v>
+      </c>
+      <c r="AA8" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="AB8" s="4" t="n">
+        <v>-0.1220198517664699</v>
+      </c>
+      <c r="AC8" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>mvo</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>always min_var</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>mvo_t_10_lw_minvar</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>mvo_t_10_lw</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="n">
+        <v>0.02692308924554491</v>
+      </c>
+      <c r="I9" s="4" t="n">
+        <v>0.7368776298813366</v>
+      </c>
+      <c r="J9" s="3" t="n">
+        <v>-0.007139675353295905</v>
+      </c>
+      <c r="K9" s="4" t="n">
+        <v>0.6573426573426573</v>
+      </c>
+      <c r="L9" s="3" t="n">
+        <v>-0.02957026320504733</v>
+      </c>
+      <c r="M9" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="N9" s="3" t="n">
+        <v>-2.236802796277855</v>
+      </c>
+      <c r="O9" s="4" t="n">
+        <v>0.7032967032967034</v>
+      </c>
+      <c r="P9" s="3" t="n">
+        <v>0.1731067727425885</v>
+      </c>
+      <c r="Q9" s="4" t="n">
+        <v>0.05394605394605394</v>
+      </c>
+      <c r="R9" s="2" t="n">
+        <v>-1930</v>
+      </c>
+      <c r="S9" s="4" t="n">
+        <v>0.2927072927072927</v>
+      </c>
+      <c r="T9" s="4" t="n">
+        <v>0.06540844339293206</v>
+      </c>
+      <c r="U9" s="4" t="n">
+        <v>0.3476523476523476</v>
+      </c>
+      <c r="V9" s="4" t="n">
+        <v>-0.1185525003602527</v>
+      </c>
+      <c r="W9" s="4" t="n">
+        <v>0.02997002997002997</v>
+      </c>
+      <c r="X9" s="3" t="n">
+        <v>0.003700524336382125</v>
+      </c>
+      <c r="Y9" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="Z9" s="3" t="n">
+        <v>0.004613403339055383</v>
+      </c>
+      <c r="AA9" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="AB9" s="4" t="n">
+        <v>-0.1916248718293949</v>
+      </c>
+      <c r="AC9" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>mvo</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>mvo_t_10_lw_changepoint_vix_cash</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>mvo_t_10_lw</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="n">
+        <v>-0.2847432325390908</v>
+      </c>
+      <c r="I10" s="4" t="n">
+        <v>0.04040843745181604</v>
+      </c>
+      <c r="J10" s="3" t="n">
+        <v>-0.06487974535555152</v>
+      </c>
+      <c r="K10" s="4" t="n">
+        <v>0.01898101898101898</v>
+      </c>
+      <c r="L10" s="3" t="n">
+        <v>-0.06602407162402024</v>
+      </c>
+      <c r="M10" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="N10" s="3" t="n">
+        <v>-10.97181177524992</v>
+      </c>
+      <c r="O10" s="4" t="n">
+        <v>0.2487512487512487</v>
+      </c>
+      <c r="P10" s="3" t="n">
+        <v>0.1080304535368612</v>
+      </c>
+      <c r="Q10" s="4" t="n">
+        <v>0.3766233766233766</v>
+      </c>
+      <c r="R10" s="2" t="n">
+        <v>-1023</v>
+      </c>
+      <c r="S10" s="4" t="n">
+        <v>0.8091908091908092</v>
+      </c>
+      <c r="T10" s="4" t="n">
+        <v>-0.1050057748826882</v>
+      </c>
+      <c r="U10" s="4" t="n">
+        <v>0.3156843156843157</v>
+      </c>
+      <c r="V10" s="4" t="n">
+        <v>-0.04219475969308892</v>
+      </c>
+      <c r="W10" s="4" t="n">
+        <v>0.6233766233766234</v>
+      </c>
+      <c r="X10" s="3" t="n">
+        <v>0.007855798073704104</v>
+      </c>
+      <c r="Y10" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="Z10" s="3" t="n">
+        <v>0.007950897049486347</v>
+      </c>
+      <c r="AA10" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="AB10" s="4" t="n">
+        <v>-0.5305037523920504</v>
+      </c>
+      <c r="AC10" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>mvo</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>hmm</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>gspc</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>mvo_t_10_lw_hmm_gspc_cash</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>mvo_t_10_lw</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="n">
+        <v>-0.1208742779274445</v>
+      </c>
+      <c r="I11" s="4" t="n">
+        <v>0.2110610093322502</v>
+      </c>
+      <c r="J11" s="3" t="n">
+        <v>-0.03448035949707222</v>
+      </c>
+      <c r="K11" s="4" t="n">
+        <v>0.09090909090909091</v>
+      </c>
+      <c r="L11" s="3" t="n">
+        <v>-0.0338814826812007</v>
+      </c>
+      <c r="M11" s="4" t="n">
+        <v>0.004995004995004995</v>
+      </c>
+      <c r="N11" s="3" t="n">
+        <v>-7.917883217809672</v>
+      </c>
+      <c r="O11" s="4" t="n">
+        <v>0.2867132867132867</v>
+      </c>
+      <c r="P11" s="3" t="n">
+        <v>-0.07618206963010365</v>
+      </c>
+      <c r="Q11" s="4" t="n">
+        <v>0.5664335664335665</v>
+      </c>
+      <c r="R11" s="2" t="n">
+        <v>293</v>
+      </c>
+      <c r="S11" s="4" t="n">
+        <v>0.6523476523476524</v>
+      </c>
+      <c r="T11" s="4" t="n">
+        <v>-0.07814843988027197</v>
+      </c>
+      <c r="U11" s="4" t="n">
+        <v>0.3406593406593407</v>
+      </c>
+      <c r="V11" s="4" t="n">
+        <v>0.05387454772573685</v>
+      </c>
+      <c r="W11" s="4" t="n">
+        <v>0.4445554445554445</v>
+      </c>
+      <c r="X11" s="3" t="n">
+        <v>0.003377215869505148</v>
+      </c>
+      <c r="Y11" s="4" t="n">
+        <v>0.001998001998001998</v>
+      </c>
+      <c r="Z11" s="3" t="n">
+        <v>0.003880699510375462</v>
+      </c>
+      <c r="AA11" s="4" t="n">
+        <v>0.01298701298701299</v>
+      </c>
+      <c r="AB11" s="4" t="n">
+        <v>-0.3146177562120781</v>
+      </c>
+      <c r="AC11" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>mvo</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>mvo_t_10_lw_wasserstein_gspc_vix_cash</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>mvo_t_10_lw</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="n">
+        <v>-0.182395858367083</v>
+      </c>
+      <c r="I12" s="4" t="n">
+        <v>0.2057320020482435</v>
+      </c>
+      <c r="J12" s="3" t="n">
+        <v>-0.05208527150935003</v>
+      </c>
+      <c r="K12" s="4" t="n">
+        <v>0.03996003996003996</v>
+      </c>
+      <c r="L12" s="3" t="n">
+        <v>-0.07024613559935507</v>
+      </c>
+      <c r="M12" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="N12" s="3" t="n">
+        <v>-9.968088250354546</v>
+      </c>
+      <c r="O12" s="4" t="n">
+        <v>0.2647352647352647</v>
+      </c>
+      <c r="P12" s="3" t="n">
+        <v>0.1545479738348267</v>
+      </c>
+      <c r="Q12" s="4" t="n">
+        <v>0.1968031968031968</v>
+      </c>
+      <c r="R12" s="2" t="n">
+        <v>-747</v>
+      </c>
+      <c r="S12" s="4" t="n">
+        <v>0.7132867132867133</v>
+      </c>
+      <c r="T12" s="4" t="n">
+        <v>-0.06281563382992077</v>
+      </c>
+      <c r="U12" s="4" t="n">
+        <v>0.5314685314685315</v>
+      </c>
+      <c r="V12" s="4" t="n">
+        <v>-0.03842221191769699</v>
+      </c>
+      <c r="W12" s="4" t="n">
+        <v>0.4785214785214785</v>
+      </c>
+      <c r="X12" s="3" t="n">
+        <v>0.007599655011870397</v>
+      </c>
+      <c r="Y12" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="Z12" s="3" t="n">
+        <v>0.008828131589852739</v>
+      </c>
+      <c r="AA12" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="AB12" s="4" t="n">
+        <v>-0.5595010709208696</v>
+      </c>
+      <c r="AC12" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>mvo</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>min_var</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>mvo_t_10_lw_changepoint_vix_min_var</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>mvo_t_10_lw</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="n">
+        <v>-0.005010301502076162</v>
+      </c>
+      <c r="I13" s="4" t="n">
+        <v>0.9311529709775367</v>
+      </c>
+      <c r="J13" s="3" t="n">
+        <v>-0.007207250839472823</v>
+      </c>
+      <c r="K13" s="4" t="n">
+        <v>0.5634365634365635</v>
+      </c>
+      <c r="L13" s="3" t="n">
+        <v>-0.01536855366174827</v>
+      </c>
+      <c r="M13" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="N13" s="3" t="n">
+        <v>-2.256148436404329</v>
+      </c>
+      <c r="O13" s="4" t="n">
+        <v>0.6153846153846154</v>
+      </c>
+      <c r="P13" s="3" t="n">
+        <v>0.1081430382287881</v>
+      </c>
+      <c r="Q13" s="4" t="n">
+        <v>0.1198801198801199</v>
+      </c>
+      <c r="R13" s="2" t="n">
+        <v>-1358</v>
+      </c>
+      <c r="S13" s="4" t="n">
+        <v>0.4095904095904096</v>
+      </c>
+      <c r="T13" s="4" t="n">
+        <v>0.02837180424669322</v>
+      </c>
+      <c r="U13" s="4" t="n">
+        <v>0.5254745254745254</v>
+      </c>
+      <c r="V13" s="4" t="n">
+        <v>-0.06902085798947896</v>
+      </c>
+      <c r="W13" s="4" t="n">
+        <v>0.1048951048951049</v>
+      </c>
+      <c r="X13" s="3" t="n">
+        <v>0.002465580039670141</v>
+      </c>
+      <c r="Y13" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="Z13" s="3" t="n">
+        <v>0.002197101211470893</v>
+      </c>
+      <c r="AA13" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="AB13" s="4" t="n">
+        <v>-0.1010508746676171</v>
+      </c>
+      <c r="AC13" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>mvo</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>hmm</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>gspc</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>min_var</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>mvo_t_10_lw_hmm_gspc_min_var</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>mvo_t_10_lw</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="n">
+        <v>-0.01389853764909193</v>
+      </c>
+      <c r="I14" s="4" t="n">
+        <v>0.7104771930752093</v>
+      </c>
+      <c r="J14" s="3" t="n">
+        <v>-0.005646630423469357</v>
+      </c>
+      <c r="K14" s="4" t="n">
+        <v>0.5114885114885115</v>
+      </c>
+      <c r="L14" s="3" t="n">
+        <v>-0.006899498801070575</v>
+      </c>
+      <c r="M14" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="N14" s="3" t="n">
+        <v>-1.801027019144129</v>
+      </c>
+      <c r="O14" s="4" t="n">
+        <v>0.5624375624375625</v>
+      </c>
+      <c r="P14" s="3" t="n">
+        <v>-0.02812844752965693</v>
+      </c>
+      <c r="Q14" s="4" t="n">
+        <v>0.7762237762237763</v>
+      </c>
+      <c r="R14" s="2" t="n">
+        <v>-275</v>
+      </c>
+      <c r="S14" s="4" t="n">
+        <v>0.5804195804195804</v>
+      </c>
+      <c r="T14" s="4" t="n">
+        <v>-0.0188359821720207</v>
+      </c>
+      <c r="U14" s="4" t="n">
+        <v>0.6223776223776224</v>
+      </c>
+      <c r="V14" s="4" t="n">
+        <v>-0.004674432644283522</v>
+      </c>
+      <c r="W14" s="4" t="n">
+        <v>0.7062937062937062</v>
+      </c>
+      <c r="X14" s="3" t="n">
+        <v>0.0008182678229806603</v>
+      </c>
+      <c r="Y14" s="4" t="n">
+        <v>0.02897102897102897</v>
+      </c>
+      <c r="Z14" s="3" t="n">
+        <v>0.00106169460169438</v>
+      </c>
+      <c r="AA14" s="4" t="n">
+        <v>0.003996003996003996</v>
+      </c>
+      <c r="AB14" s="4" t="n">
+        <v>-0.04823546173906246</v>
+      </c>
+      <c r="AC14" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>mvo</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>min_var</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>mvo_t_10_lw_wasserstein_gspc_vix_min_var</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>mvo_t_10_lw</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="n">
+        <v>0.01088267683938749</v>
+      </c>
+      <c r="I15" s="4" t="n">
+        <v>0.850973840409305</v>
+      </c>
+      <c r="J15" s="3" t="n">
+        <v>-0.004417607144387478</v>
+      </c>
+      <c r="K15" s="4" t="n">
+        <v>0.7182817182817183</v>
+      </c>
+      <c r="L15" s="3" t="n">
+        <v>-0.01611415438435287</v>
+      </c>
+      <c r="M15" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="N15" s="3" t="n">
+        <v>-1.430062768064642</v>
+      </c>
+      <c r="O15" s="4" t="n">
+        <v>0.7222777222777222</v>
+      </c>
+      <c r="P15" s="3" t="n">
+        <v>0.0447826176125381</v>
+      </c>
+      <c r="Q15" s="4" t="n">
+        <v>0.2367632367632368</v>
+      </c>
+      <c r="R15" s="2" t="n">
+        <v>-1338</v>
+      </c>
+      <c r="S15" s="4" t="n">
+        <v>0.3686313686313686</v>
+      </c>
+      <c r="T15" s="4" t="n">
+        <v>0.007357315511766271</v>
+      </c>
+      <c r="U15" s="4" t="n">
+        <v>0.8631368631368631</v>
+      </c>
+      <c r="V15" s="4" t="n">
+        <v>-0.05619528533037027</v>
+      </c>
+      <c r="W15" s="4" t="n">
+        <v>0.06493506493506493</v>
+      </c>
+      <c r="X15" s="3" t="n">
+        <v>0.002489094648211176</v>
+      </c>
+      <c r="Y15" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="Z15" s="3" t="n">
+        <v>0.002492461085531895</v>
+      </c>
+      <c r="AA15" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="AB15" s="4" t="n">
+        <v>-0.105485286656933</v>
+      </c>
+      <c r="AC15" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>mvo</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>always min_var</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>mvo_t_10_lw_minvar</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>mvo_t_10_lw</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="n">
+        <v>0.02190235106292368</v>
+      </c>
+      <c r="I16" s="4" t="n">
+        <v>0.7747812705888728</v>
+      </c>
+      <c r="J16" s="3" t="n">
+        <v>-0.008873272815828295</v>
+      </c>
+      <c r="K16" s="4" t="n">
+        <v>0.6013986013986014</v>
+      </c>
+      <c r="L16" s="3" t="n">
+        <v>-0.0331360374664858</v>
+      </c>
+      <c r="M16" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="N16" s="3" t="n">
+        <v>-2.578122186174085</v>
+      </c>
+      <c r="O16" s="4" t="n">
+        <v>0.6423576423576424</v>
+      </c>
+      <c r="P16" s="3" t="n">
+        <v>0.1400184333660996</v>
+      </c>
+      <c r="Q16" s="4" t="n">
+        <v>0.08191808191808192</v>
+      </c>
+      <c r="R16" s="2" t="n">
+        <v>-2219</v>
+      </c>
+      <c r="S16" s="4" t="n">
+        <v>0.3166833166833167</v>
+      </c>
+      <c r="T16" s="4" t="n">
+        <v>0.03907895576786427</v>
+      </c>
+      <c r="U16" s="4" t="n">
+        <v>0.5124875124875125</v>
+      </c>
+      <c r="V16" s="4" t="n">
+        <v>-0.1232349460591586</v>
+      </c>
+      <c r="W16" s="4" t="n">
+        <v>0.04595404595404595</v>
+      </c>
+      <c r="X16" s="3" t="n">
+        <v>0.003872509450087559</v>
+      </c>
+      <c r="Y16" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="Z16" s="3" t="n">
+        <v>0.00494834604131577</v>
+      </c>
+      <c r="AA16" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="AB16" s="4" t="n">
+        <v>-0.2051768563174912</v>
+      </c>
+      <c r="AC16" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>mvo</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>mvo_t_10_lw_changepoint_vix_cash</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>mvo_t_10_lw</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="n">
+        <v>0.03981877878873152</v>
+      </c>
+      <c r="I17" s="4" t="n">
+        <v>0.7817915307334559</v>
+      </c>
+      <c r="J17" s="3" t="n">
+        <v>-0.0216471019145245</v>
+      </c>
+      <c r="K17" s="4" t="n">
+        <v>0.4035964035964036</v>
+      </c>
+      <c r="L17" s="3" t="n">
+        <v>-0.07063834875815125</v>
+      </c>
+      <c r="M17" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="N17" s="3" t="n">
+        <v>-5.421081372417188</v>
+      </c>
+      <c r="O17" s="4" t="n">
+        <v>0.5164835164835165</v>
+      </c>
+      <c r="P17" s="3" t="n">
+        <v>0.2369429674159471</v>
+      </c>
+      <c r="Q17" s="4" t="n">
+        <v>0.04495504495504495</v>
+      </c>
+      <c r="R17" s="2" t="n">
+        <v>-1378</v>
+      </c>
+      <c r="S17" s="4" t="n">
+        <v>0.3826173826173826</v>
+      </c>
+      <c r="T17" s="4" t="n">
+        <v>0.06540318635809494</v>
+      </c>
+      <c r="U17" s="4" t="n">
+        <v>0.5494505494505495</v>
+      </c>
+      <c r="V17" s="4" t="n">
+        <v>-0.1143037797303506</v>
+      </c>
+      <c r="W17" s="4" t="n">
+        <v>0.04195804195804196</v>
+      </c>
+      <c r="X17" s="3" t="n">
+        <v>0.008476167634931579</v>
+      </c>
+      <c r="Y17" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="Z17" s="3" t="n">
+        <v>0.008639711424833319</v>
+      </c>
+      <c r="AA17" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="AB17" s="4" t="n">
+        <v>-0.5702128673460041</v>
+      </c>
+      <c r="AC17" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>mvo</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>hmm</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>gspc</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>mvo_t_10_lw_hmm_gspc_cash</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>mvo_t_10_lw</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="n">
+        <v>-0.03172995829168238</v>
+      </c>
+      <c r="I18" s="4" t="n">
+        <v>0.6615781008765117</v>
+      </c>
+      <c r="J18" s="3" t="n">
+        <v>-0.01459033692855559</v>
+      </c>
+      <c r="K18" s="4" t="n">
+        <v>0.3596403596403596</v>
+      </c>
+      <c r="L18" s="3" t="n">
+        <v>-0.02217554797285165</v>
+      </c>
+      <c r="M18" s="4" t="n">
+        <v>0.01798201798201798</v>
+      </c>
+      <c r="N18" s="3" t="n">
+        <v>-3.962894003545257</v>
+      </c>
+      <c r="O18" s="4" t="n">
+        <v>0.4595404595404595</v>
+      </c>
+      <c r="P18" s="3" t="n">
+        <v>0.0100738711248034</v>
+      </c>
+      <c r="Q18" s="4" t="n">
+        <v>0.8271728271728271</v>
+      </c>
+      <c r="R18" s="2" t="n">
+        <v>-570</v>
+      </c>
+      <c r="S18" s="4" t="n">
+        <v>0.6543456543456544</v>
+      </c>
+      <c r="T18" s="4" t="n">
+        <v>-0.0241053327247838</v>
+      </c>
+      <c r="U18" s="4" t="n">
+        <v>0.6893106893106893</v>
+      </c>
+      <c r="V18" s="4" t="n">
+        <v>-0.02435568519849585</v>
+      </c>
+      <c r="W18" s="4" t="n">
+        <v>0.4605394605394605</v>
+      </c>
+      <c r="X18" s="3" t="n">
+        <v>0.001443349671667243</v>
+      </c>
+      <c r="Y18" s="4" t="n">
+        <v>0.06093906093906094</v>
+      </c>
+      <c r="Z18" s="3" t="n">
+        <v>0.002364685587027172</v>
+      </c>
+      <c r="AA18" s="4" t="n">
+        <v>0.05494505494505494</v>
+      </c>
+      <c r="AB18" s="4" t="n">
+        <v>-0.2072179768594357</v>
+      </c>
+      <c r="AC18" s="4" t="n">
+        <v>0.003996003996003996</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>mvo</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>mvo_t_10_lw_wasserstein_gspc_vix_cash</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>mvo_t_10_lw</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="n">
+        <v>-0.03689728534554564</v>
+      </c>
+      <c r="I19" s="4" t="n">
+        <v>0.7713893610864664</v>
+      </c>
+      <c r="J19" s="3" t="n">
+        <v>-0.02710673270903687</v>
+      </c>
+      <c r="K19" s="4" t="n">
+        <v>0.2517482517482518</v>
+      </c>
+      <c r="L19" s="3" t="n">
+        <v>-0.05606148008249312</v>
+      </c>
+      <c r="M19" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="N19" s="3" t="n">
+        <v>-6.384830314192427</v>
+      </c>
+      <c r="O19" s="4" t="n">
+        <v>0.4055944055944056</v>
+      </c>
+      <c r="P19" s="3" t="n">
+        <v>0.07657879420467995</v>
+      </c>
+      <c r="Q19" s="4" t="n">
+        <v>0.3576423576423576</v>
+      </c>
+      <c r="R19" s="2" t="n">
+        <v>-428</v>
+      </c>
+      <c r="S19" s="4" t="n">
+        <v>0.5864135864135864</v>
+      </c>
+      <c r="T19" s="4" t="n">
+        <v>-0.02935665479175237</v>
+      </c>
+      <c r="U19" s="4" t="n">
+        <v>0.7392607392607392</v>
+      </c>
+      <c r="V19" s="4" t="n">
+        <v>-0.05538583755654372</v>
+      </c>
+      <c r="W19" s="4" t="n">
+        <v>0.1918081918081918</v>
+      </c>
+      <c r="X19" s="3" t="n">
+        <v>0.005859570075166517</v>
+      </c>
+      <c r="Y19" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="Z19" s="3" t="n">
+        <v>0.006622740115161549</v>
+      </c>
+      <c r="AA19" s="4" t="n">
+        <v>0.003996003996003996</v>
+      </c>
+      <c r="AB19" s="4" t="n">
+        <v>-0.4673731425639131</v>
+      </c>
+      <c r="AC19" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>mvo</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>min_var</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>mvo_t_10_lw_changepoint_vix_min_var</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>mvo_t_10_lw</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="n">
+        <v>0.04875483922733259</v>
+      </c>
+      <c r="I20" s="4" t="n">
+        <v>0.3671193068291868</v>
+      </c>
+      <c r="J20" s="3" t="n">
+        <v>0.002820817243463156</v>
+      </c>
+      <c r="K20" s="4" t="n">
+        <v>0.8061938061938062</v>
+      </c>
+      <c r="L20" s="3" t="n">
+        <v>-0.0175120795844996</v>
+      </c>
+      <c r="M20" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="N20" s="3" t="n">
+        <v>0.9449407327148087</v>
+      </c>
+      <c r="O20" s="4" t="n">
+        <v>0.7382617382617382</v>
+      </c>
+      <c r="P20" s="3" t="n">
+        <v>0.08953671047454803</v>
+      </c>
+      <c r="Q20" s="4" t="n">
+        <v>0.0919080919080919</v>
+      </c>
+      <c r="R20" s="2" t="n">
+        <v>-1249</v>
+      </c>
+      <c r="S20" s="4" t="n">
+        <v>0.2767232767232767</v>
+      </c>
+      <c r="T20" s="4" t="n">
+        <v>0.04097707020897898</v>
+      </c>
+      <c r="U20" s="4" t="n">
+        <v>0.3086913086913087</v>
+      </c>
+      <c r="V20" s="4" t="n">
+        <v>-0.06208737844340362</v>
+      </c>
+      <c r="W20" s="4" t="n">
+        <v>0.04295704295704296</v>
+      </c>
+      <c r="X20" s="3" t="n">
+        <v>0.002126105147593368</v>
+      </c>
+      <c r="Y20" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="Z20" s="3" t="n">
+        <v>0.002344271597193543</v>
+      </c>
+      <c r="AA20" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="AB20" s="4" t="n">
+        <v>-0.1081810025265966</v>
+      </c>
+      <c r="AC20" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>mvo</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>hmm</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>gspc</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>min_var</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>mvo_t_10_lw_hmm_gspc_min_var</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>mvo_t_10_lw</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="n">
+        <v>-0.01364094942731665</v>
+      </c>
+      <c r="I21" s="4" t="n">
+        <v>0.6600650285973337</v>
+      </c>
+      <c r="J21" s="3" t="n">
+        <v>-0.005025448358404461</v>
+      </c>
+      <c r="K21" s="4" t="n">
+        <v>0.5114885114885115</v>
+      </c>
+      <c r="L21" s="3" t="n">
+        <v>-0.00560001713431213</v>
+      </c>
+      <c r="M21" s="4" t="n">
+        <v>0.008991008991008992</v>
+      </c>
+      <c r="N21" s="3" t="n">
+        <v>-1.529142374919912</v>
+      </c>
+      <c r="O21" s="4" t="n">
+        <v>0.5694305694305695</v>
+      </c>
+      <c r="P21" s="3" t="n">
+        <v>0.0100738711248034</v>
+      </c>
+      <c r="Q21" s="4" t="n">
+        <v>0.7172827172827173</v>
+      </c>
+      <c r="R21" s="2" t="n">
+        <v>-88</v>
+      </c>
+      <c r="S21" s="4" t="n">
+        <v>0.7252747252747253</v>
+      </c>
+      <c r="T21" s="4" t="n">
+        <v>-0.00612304954434123</v>
+      </c>
+      <c r="U21" s="4" t="n">
+        <v>0.7992007992007992</v>
+      </c>
+      <c r="V21" s="4" t="n">
+        <v>-0.01051560540410151</v>
+      </c>
+      <c r="W21" s="4" t="n">
+        <v>0.4255744255744256</v>
+      </c>
+      <c r="X21" s="3" t="n">
+        <v>0.0004830344313913673</v>
+      </c>
+      <c r="Y21" s="4" t="n">
+        <v>0.04795204795204795</v>
+      </c>
+      <c r="Z21" s="3" t="n">
+        <v>0.0005902419414877888</v>
+      </c>
+      <c r="AA21" s="4" t="n">
+        <v>0.02997002997002997</v>
+      </c>
+      <c r="AB21" s="4" t="n">
+        <v>-0.03516476952004866</v>
+      </c>
+      <c r="AC21" s="4" t="n">
+        <v>0.008991008991008992</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>mvo</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>min_var</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>mvo_t_10_lw_wasserstein_gspc_vix_min_var</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>mvo_t_10_lw</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="n">
+        <v>0.01915358782294158</v>
+      </c>
+      <c r="I22" s="4" t="n">
+        <v>0.7087994779463802</v>
+      </c>
+      <c r="J22" s="3" t="n">
+        <v>-0.001941573614454434</v>
+      </c>
+      <c r="K22" s="4" t="n">
+        <v>0.8561438561438561</v>
+      </c>
+      <c r="L22" s="3" t="n">
+        <v>-0.01489058252714881</v>
+      </c>
+      <c r="M22" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="N22" s="3" t="n">
+        <v>-0.6133400185135365</v>
+      </c>
+      <c r="O22" s="4" t="n">
+        <v>0.8441558441558441</v>
+      </c>
+      <c r="P22" s="3" t="n">
+        <v>0.04753111959218548</v>
+      </c>
+      <c r="Q22" s="4" t="n">
+        <v>0.2337662337662338</v>
+      </c>
+      <c r="R22" s="2" t="n">
+        <v>-296</v>
+      </c>
+      <c r="S22" s="4" t="n">
+        <v>0.4875124875124875</v>
+      </c>
+      <c r="T22" s="4" t="n">
+        <v>0.0129496649190137</v>
+      </c>
+      <c r="U22" s="4" t="n">
+        <v>0.7342657342657343</v>
+      </c>
+      <c r="V22" s="4" t="n">
+        <v>-0.04292923522993639</v>
+      </c>
+      <c r="W22" s="4" t="n">
+        <v>0.07592407592407592</v>
+      </c>
+      <c r="X22" s="3" t="n">
+        <v>0.00174611249125901</v>
+      </c>
+      <c r="Y22" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="Z22" s="3" t="n">
+        <v>0.002225511777561567</v>
+      </c>
+      <c r="AA22" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="AB22" s="4" t="n">
+        <v>-0.09215619834534605</v>
+      </c>
+      <c r="AC22" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward_changepoint_vix_cash</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="n">
+        <v>-0.2023642087111063</v>
+      </c>
+      <c r="I23" s="4" t="n">
+        <v>0.1474103056270371</v>
+      </c>
+      <c r="J23" s="3" t="n">
+        <v>-0.05051514886047429</v>
+      </c>
+      <c r="K23" s="4" t="n">
+        <v>0.03296703296703297</v>
+      </c>
+      <c r="L23" s="3" t="n">
+        <v>-0.06283876154767598</v>
+      </c>
+      <c r="M23" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="N23" s="3" t="n">
+        <v>-9.048483544826571</v>
+      </c>
+      <c r="O23" s="4" t="n">
+        <v>0.2277722277722278</v>
+      </c>
+      <c r="P23" s="3" t="n">
+        <v>0.07188382530363513</v>
+      </c>
+      <c r="Q23" s="4" t="n">
+        <v>0.4655344655344655</v>
+      </c>
+      <c r="R23" s="2" t="n">
+        <v>332</v>
+      </c>
+      <c r="S23" s="4" t="n">
+        <v>0.6323676323676324</v>
+      </c>
+      <c r="T23" s="4" t="n">
+        <v>-0.0929244978741107</v>
+      </c>
+      <c r="U23" s="4" t="n">
+        <v>0.3886113886113886</v>
+      </c>
+      <c r="V23" s="4" t="n">
+        <v>0.00602329350633081</v>
+      </c>
+      <c r="W23" s="4" t="n">
+        <v>0.8901098901098901</v>
+      </c>
+      <c r="X23" s="3" t="n">
+        <v>0.00668204279376065</v>
+      </c>
+      <c r="Y23" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="Z23" s="3" t="n">
+        <v>0.008096519166346787</v>
+      </c>
+      <c r="AA23" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="AB23" s="4" t="n">
+        <v>-0.4844271558699712</v>
+      </c>
+      <c r="AC23" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>hmm</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>gspc</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward_hmm_gspc_cash</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="n">
+        <v>-0.08125926962809034</v>
+      </c>
+      <c r="I24" s="4" t="n">
+        <v>0.5174123016776782</v>
+      </c>
+      <c r="J24" s="3" t="n">
+        <v>-0.03165416945079683</v>
+      </c>
+      <c r="K24" s="4" t="n">
+        <v>0.05394605394605394</v>
+      </c>
+      <c r="L24" s="3" t="n">
+        <v>-0.04808500456408087</v>
+      </c>
+      <c r="M24" s="4" t="n">
+        <v>0.002997002997002997</v>
+      </c>
+      <c r="N24" s="3" t="n">
+        <v>-6.908675110776386</v>
+      </c>
+      <c r="O24" s="4" t="n">
+        <v>0.2487512487512487</v>
+      </c>
+      <c r="P24" s="3" t="n">
+        <v>0.03511321691641112</v>
+      </c>
+      <c r="Q24" s="4" t="n">
+        <v>0.7032967032967034</v>
+      </c>
+      <c r="R24" s="2" t="n">
+        <v>589</v>
+      </c>
+      <c r="S24" s="4" t="n">
+        <v>0.3986013986013986</v>
+      </c>
+      <c r="T24" s="4" t="n">
+        <v>-0.0580130285169323</v>
+      </c>
+      <c r="U24" s="4" t="n">
+        <v>0.5004995004995005</v>
+      </c>
+      <c r="V24" s="4" t="n">
+        <v>0.03108687641651435</v>
+      </c>
+      <c r="W24" s="4" t="n">
+        <v>0.5474525474525475</v>
+      </c>
+      <c r="X24" s="3" t="n">
+        <v>0.003538827178292476</v>
+      </c>
+      <c r="Y24" s="4" t="n">
+        <v>0.005994005994005994</v>
+      </c>
+      <c r="Z24" s="3" t="n">
+        <v>0.006141245408139595</v>
+      </c>
+      <c r="AA24" s="4" t="n">
+        <v>0.006993006993006993</v>
+      </c>
+      <c r="AB24" s="4" t="n">
+        <v>-0.3908211806434154</v>
+      </c>
+      <c r="AC24" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_cash</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="n">
+        <v>-0.05674482381857038</v>
+      </c>
+      <c r="I25" s="4" t="n">
+        <v>0.7239897333165021</v>
+      </c>
+      <c r="J25" s="3" t="n">
+        <v>-0.03964013019895599</v>
+      </c>
+      <c r="K25" s="4" t="n">
+        <v>0.05994005994005994</v>
+      </c>
+      <c r="L25" s="3" t="n">
+        <v>-0.0787524950428391</v>
+      </c>
+      <c r="M25" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="N25" s="3" t="n">
+        <v>-7.941623148817495</v>
+      </c>
+      <c r="O25" s="4" t="n">
+        <v>0.2507492507492508</v>
+      </c>
+      <c r="P25" s="3" t="n">
+        <v>0.2526986594708295</v>
+      </c>
+      <c r="Q25" s="4" t="n">
+        <v>0.03896103896103896</v>
+      </c>
+      <c r="R25" s="2" t="n">
+        <v>-174</v>
+      </c>
+      <c r="S25" s="4" t="n">
+        <v>0.7942057942057942</v>
+      </c>
+      <c r="T25" s="4" t="n">
+        <v>0.06168734601679982</v>
+      </c>
+      <c r="U25" s="4" t="n">
+        <v>0.6463536463536463</v>
+      </c>
+      <c r="V25" s="4" t="n">
+        <v>-0.03525710559497153</v>
+      </c>
+      <c r="W25" s="4" t="n">
+        <v>0.3136863136863137</v>
+      </c>
+      <c r="X25" s="3" t="n">
+        <v>0.006625596228986891</v>
+      </c>
+      <c r="Y25" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="Z25" s="3" t="n">
+        <v>0.01028463679958158</v>
+      </c>
+      <c r="AA25" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="AB25" s="4" t="n">
+        <v>-0.5676330150746547</v>
+      </c>
+      <c r="AC25" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>min_var</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward_changepoint_vix_min_var</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="n">
+        <v>0.001728227762052471</v>
+      </c>
+      <c r="I26" s="4" t="n">
+        <v>0.9437801204654567</v>
+      </c>
+      <c r="J26" s="3" t="n">
+        <v>-0.001919953082912679</v>
+      </c>
+      <c r="K26" s="4" t="n">
+        <v>0.6863136863136863</v>
+      </c>
+      <c r="L26" s="3" t="n">
+        <v>-0.005090990058101458</v>
+      </c>
+      <c r="M26" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="N26" s="3" t="n">
+        <v>-0.5911523297351522</v>
+      </c>
+      <c r="O26" s="4" t="n">
+        <v>0.6933066933066933</v>
+      </c>
+      <c r="P26" s="3" t="n">
+        <v>0.08132006789915791</v>
+      </c>
+      <c r="Q26" s="4" t="n">
+        <v>0.1898101898101898</v>
+      </c>
+      <c r="R26" s="2" t="n">
+        <v>-79</v>
+      </c>
+      <c r="S26" s="4" t="n">
+        <v>0.5634365634365635</v>
+      </c>
+      <c r="T26" s="4" t="n">
+        <v>0.0397041075879539</v>
+      </c>
+      <c r="U26" s="4" t="n">
+        <v>0.3726273726273726</v>
+      </c>
+      <c r="V26" s="4" t="n">
+        <v>-0.01933628547664387</v>
+      </c>
+      <c r="W26" s="4" t="n">
+        <v>0.1608391608391608</v>
+      </c>
+      <c r="X26" s="3" t="n">
+        <v>0.0004710085521917665</v>
+      </c>
+      <c r="Y26" s="4" t="n">
+        <v>0.04095904095904096</v>
+      </c>
+      <c r="Z26" s="3" t="n">
+        <v>0.0008461497086628203</v>
+      </c>
+      <c r="AA26" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="AB26" s="4" t="n">
+        <v>-0.04327457936738077</v>
+      </c>
+      <c r="AC26" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>hmm</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>gspc</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>min_var</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward_hmm_gspc_min_var</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="n">
+        <v>0.00244483292983873</v>
+      </c>
+      <c r="I27" s="4" t="n">
+        <v>0.8842863098494348</v>
+      </c>
+      <c r="J27" s="3" t="n">
+        <v>-0.001359056743453158</v>
+      </c>
+      <c r="K27" s="4" t="n">
+        <v>0.6023976023976024</v>
+      </c>
+      <c r="L27" s="3" t="n">
+        <v>-0.004114254085149122</v>
+      </c>
+      <c r="M27" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="N27" s="3" t="n">
+        <v>-0.4213360863195987</v>
+      </c>
+      <c r="O27" s="4" t="n">
+        <v>0.6393606393606394</v>
+      </c>
+      <c r="P27" s="3" t="n">
+        <v>0.04253180038609494</v>
+      </c>
+      <c r="Q27" s="4" t="n">
+        <v>0.1958041958041958</v>
+      </c>
+      <c r="R27" s="2" t="n">
+        <v>-15</v>
+      </c>
+      <c r="S27" s="4" t="n">
+        <v>0.7532467532467533</v>
+      </c>
+      <c r="T27" s="4" t="n">
+        <v>0.01795814545541816</v>
+      </c>
+      <c r="U27" s="4" t="n">
+        <v>0.3976023976023976</v>
+      </c>
+      <c r="V27" s="4" t="n">
+        <v>-0.006873361301410558</v>
+      </c>
+      <c r="W27" s="4" t="n">
+        <v>0.2697302697302698</v>
+      </c>
+      <c r="X27" s="3" t="n">
+        <v>0.00042864151641454</v>
+      </c>
+      <c r="Y27" s="4" t="n">
+        <v>0.008991008991008992</v>
+      </c>
+      <c r="Z27" s="3" t="n">
+        <v>0.0006075873428013946</v>
+      </c>
+      <c r="AA27" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="AB27" s="4" t="n">
+        <v>-0.03019392865293036</v>
+      </c>
+      <c r="AC27" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>min_var</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_min_var</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="n">
+        <v>-0.01412670161143676</v>
+      </c>
+      <c r="I28" s="4" t="n">
+        <v>0.5674196914125045</v>
+      </c>
+      <c r="J28" s="3" t="n">
+        <v>-0.004945240187505098</v>
+      </c>
+      <c r="K28" s="4" t="n">
+        <v>0.2027972027972028</v>
+      </c>
+      <c r="L28" s="3" t="n">
+        <v>-0.005433907215115136</v>
+      </c>
+      <c r="M28" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="N28" s="3" t="n">
+        <v>-1.467617773027849</v>
+      </c>
+      <c r="O28" s="4" t="n">
+        <v>0.3416583416583416</v>
+      </c>
+      <c r="P28" s="3" t="n">
+        <v>0.05115102107239644</v>
+      </c>
+      <c r="Q28" s="4" t="n">
+        <v>0.2067932067932068</v>
+      </c>
+      <c r="R28" s="2" t="n">
+        <v>195</v>
+      </c>
+      <c r="S28" s="4" t="n">
+        <v>0.5854145854145855</v>
+      </c>
+      <c r="T28" s="4" t="n">
+        <v>0.01387559359712506</v>
+      </c>
+      <c r="U28" s="4" t="n">
+        <v>0.6533466533466533</v>
+      </c>
+      <c r="V28" s="4" t="n">
+        <v>-0.008427197581062876</v>
+      </c>
+      <c r="W28" s="4" t="n">
+        <v>0.3426573426573427</v>
+      </c>
+      <c r="X28" s="3" t="n">
+        <v>0.0004848428995915515</v>
+      </c>
+      <c r="Y28" s="4" t="n">
+        <v>0.01598401598401598</v>
+      </c>
+      <c r="Z28" s="3" t="n">
+        <v>0.0007628047377875348</v>
+      </c>
+      <c r="AA28" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="AB28" s="4" t="n">
+        <v>-0.04665159541453601</v>
+      </c>
+      <c r="AC28" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward_changepoint_vix_cash</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="H29" s="4" t="n">
+        <v>-0.2826224909017265</v>
+      </c>
+      <c r="I29" s="4" t="n">
+        <v>0.03867642926581932</v>
+      </c>
+      <c r="J29" s="3" t="n">
+        <v>-0.06001313528932202</v>
+      </c>
+      <c r="K29" s="4" t="n">
+        <v>0.00999000999000999</v>
+      </c>
+      <c r="L29" s="3" t="n">
+        <v>-0.06087377415385037</v>
+      </c>
+      <c r="M29" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="N29" s="3" t="n">
+        <v>-10.19936646482919</v>
+      </c>
+      <c r="O29" s="4" t="n">
+        <v>0.2017982017982018</v>
+      </c>
+      <c r="P29" s="3" t="n">
+        <v>0.06089211151807894</v>
+      </c>
+      <c r="Q29" s="4" t="n">
+        <v>0.5344655344655345</v>
+      </c>
+      <c r="R29" s="2" t="n">
+        <v>474</v>
+      </c>
+      <c r="S29" s="4" t="n">
+        <v>0.5554445554445554</v>
+      </c>
+      <c r="T29" s="4" t="n">
+        <v>-0.1223853438335795</v>
+      </c>
+      <c r="U29" s="4" t="n">
+        <v>0.2727272727272727</v>
+      </c>
+      <c r="V29" s="4" t="n">
+        <v>0.01586967180495924</v>
+      </c>
+      <c r="W29" s="4" t="n">
+        <v>0.7652347652347652</v>
+      </c>
+      <c r="X29" s="3" t="n">
+        <v>0.006313713406598684</v>
+      </c>
+      <c r="Y29" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="Z29" s="3" t="n">
+        <v>0.007519020037100237</v>
+      </c>
+      <c r="AA29" s="4" t="n">
+        <v>0.002997002997002997</v>
+      </c>
+      <c r="AB29" s="4" t="n">
+        <v>-0.471622967233023</v>
+      </c>
+      <c r="AC29" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>hmm</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>gspc</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward_hmm_gspc_cash</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="n">
+        <v>-0.1185894736679695</v>
+      </c>
+      <c r="I30" s="4" t="n">
+        <v>0.2242365153519348</v>
+      </c>
+      <c r="J30" s="3" t="n">
+        <v>-0.03251262458940359</v>
+      </c>
+      <c r="K30" s="4" t="n">
+        <v>0.05394605394605394</v>
+      </c>
+      <c r="L30" s="3" t="n">
+        <v>-0.03343123684365831</v>
+      </c>
+      <c r="M30" s="4" t="n">
+        <v>0.005994005994005994</v>
+      </c>
+      <c r="N30" s="3" t="n">
+        <v>-7.320686816965648</v>
+      </c>
+      <c r="O30" s="4" t="n">
+        <v>0.2317682317682318</v>
+      </c>
+      <c r="P30" s="3" t="n">
+        <v>0.02381572792547004</v>
+      </c>
+      <c r="Q30" s="4" t="n">
+        <v>0.7712287712287712</v>
+      </c>
+      <c r="R30" s="2" t="n">
+        <v>609</v>
+      </c>
+      <c r="S30" s="4" t="n">
+        <v>0.4015984015984016</v>
+      </c>
+      <c r="T30" s="4" t="n">
+        <v>-0.065159535433893</v>
+      </c>
+      <c r="U30" s="4" t="n">
+        <v>0.4645354645354645</v>
+      </c>
+      <c r="V30" s="4" t="n">
+        <v>0.02537420289536947</v>
+      </c>
+      <c r="W30" s="4" t="n">
+        <v>0.5124875124875125</v>
+      </c>
+      <c r="X30" s="3" t="n">
+        <v>0.00250101088682188</v>
+      </c>
+      <c r="Y30" s="4" t="n">
+        <v>0.01298701298701299</v>
+      </c>
+      <c r="Z30" s="3" t="n">
+        <v>0.003955481103950165</v>
+      </c>
+      <c r="AA30" s="4" t="n">
+        <v>0.01598401598401598</v>
+      </c>
+      <c r="AB30" s="4" t="n">
+        <v>-0.2899902893061611</v>
+      </c>
+      <c r="AC30" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_cash</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="H31" s="4" t="n">
+        <v>-0.2135569158185108</v>
+      </c>
+      <c r="I31" s="4" t="n">
+        <v>0.1323519367002267</v>
+      </c>
+      <c r="J31" s="3" t="n">
+        <v>-0.05277276264913092</v>
+      </c>
+      <c r="K31" s="4" t="n">
+        <v>0.01498501498501499</v>
+      </c>
+      <c r="L31" s="3" t="n">
+        <v>-0.06445990851788742</v>
+      </c>
+      <c r="M31" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="N31" s="3" t="n">
+        <v>-9.626464195469691</v>
+      </c>
+      <c r="O31" s="4" t="n">
+        <v>0.2027972027972028</v>
+      </c>
+      <c r="P31" s="3" t="n">
+        <v>0.1537374355353038</v>
+      </c>
+      <c r="Q31" s="4" t="n">
+        <v>0.2057942057942058</v>
+      </c>
+      <c r="R31" s="2" t="n">
+        <v>416</v>
+      </c>
+      <c r="S31" s="4" t="n">
+        <v>0.5424575424575424</v>
+      </c>
+      <c r="T31" s="4" t="n">
+        <v>-0.06762196318479186</v>
+      </c>
+      <c r="U31" s="4" t="n">
+        <v>0.5604395604395604</v>
+      </c>
+      <c r="V31" s="4" t="n">
+        <v>-0.005859407009982984</v>
+      </c>
+      <c r="W31" s="4" t="n">
+        <v>0.8781218781218781</v>
+      </c>
+      <c r="X31" s="3" t="n">
+        <v>0.005992152403898441</v>
+      </c>
+      <c r="Y31" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="Z31" s="3" t="n">
+        <v>0.008173707923430217</v>
+      </c>
+      <c r="AA31" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="AB31" s="4" t="n">
+        <v>-0.4960898617128426</v>
+      </c>
+      <c r="AC31" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>min_var</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward_changepoint_vix_min_var</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="n">
+        <v>0.001729965229601702</v>
+      </c>
+      <c r="I32" s="4" t="n">
+        <v>0.9418113816562546</v>
+      </c>
+      <c r="J32" s="3" t="n">
+        <v>-0.001916681972182629</v>
+      </c>
+      <c r="K32" s="4" t="n">
+        <v>0.6873126873126874</v>
+      </c>
+      <c r="L32" s="3" t="n">
+        <v>-0.004978520152714772</v>
+      </c>
+      <c r="M32" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="N32" s="3" t="n">
+        <v>-0.6142679444125996</v>
+      </c>
+      <c r="O32" s="4" t="n">
+        <v>0.7032967032967034</v>
+      </c>
+      <c r="P32" s="3" t="n">
+        <v>0.07648403652350844</v>
+      </c>
+      <c r="Q32" s="4" t="n">
+        <v>0.1778221778221778</v>
+      </c>
+      <c r="R32" s="2" t="n">
+        <v>-18</v>
+      </c>
+      <c r="S32" s="4" t="n">
+        <v>0.7652347652347652</v>
+      </c>
+      <c r="T32" s="4" t="n">
+        <v>0.03965509891465249</v>
+      </c>
+      <c r="U32" s="4" t="n">
+        <v>0.3616383616383617</v>
+      </c>
+      <c r="V32" s="4" t="n">
+        <v>-0.01677752598783767</v>
+      </c>
+      <c r="W32" s="4" t="n">
+        <v>0.1478521478521478</v>
+      </c>
+      <c r="X32" s="3" t="n">
+        <v>0.0004221757450168038</v>
+      </c>
+      <c r="Y32" s="4" t="n">
+        <v>0.04695304695304695</v>
+      </c>
+      <c r="Z32" s="3" t="n">
+        <v>0.0007946808531444811</v>
+      </c>
+      <c r="AA32" s="4" t="n">
+        <v>0.001998001998001998</v>
+      </c>
+      <c r="AB32" s="4" t="n">
+        <v>-0.04223430528700289</v>
+      </c>
+      <c r="AC32" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>hmm</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>gspc</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>min_var</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward_hmm_gspc_min_var</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="H33" s="4" t="n">
+        <v>-0.01019608194916713</v>
+      </c>
+      <c r="I33" s="4" t="n">
+        <v>0.5391838511066329</v>
+      </c>
+      <c r="J33" s="3" t="n">
+        <v>-0.003205188641602075</v>
+      </c>
+      <c r="K33" s="4" t="n">
+        <v>0.3156843156843157</v>
+      </c>
+      <c r="L33" s="3" t="n">
+        <v>-0.002945243499505368</v>
+      </c>
+      <c r="M33" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="N33" s="3" t="n">
+        <v>-1.011213323686157</v>
+      </c>
+      <c r="O33" s="4" t="n">
+        <v>0.4295704295704296</v>
+      </c>
+      <c r="P33" s="3" t="n">
+        <v>0.04388962311296407</v>
+      </c>
+      <c r="Q33" s="4" t="n">
+        <v>0.2997002997002997</v>
+      </c>
+      <c r="R33" s="2" t="n">
+        <v>-13</v>
+      </c>
+      <c r="S33" s="4" t="n">
+        <v>0.7952047952047953</v>
+      </c>
+      <c r="T33" s="4" t="n">
+        <v>0.01563980215232191</v>
+      </c>
+      <c r="U33" s="4" t="n">
+        <v>0.5804195804195804</v>
+      </c>
+      <c r="V33" s="4" t="n">
+        <v>-0.008320880614767365</v>
+      </c>
+      <c r="W33" s="4" t="n">
+        <v>0.3396603396603396</v>
+      </c>
+      <c r="X33" s="3" t="n">
+        <v>0.0002964325656300143</v>
+      </c>
+      <c r="Y33" s="4" t="n">
+        <v>0.05394605394605394</v>
+      </c>
+      <c r="Z33" s="3" t="n">
+        <v>0.0004530829719151773</v>
+      </c>
+      <c r="AA33" s="4" t="n">
+        <v>0.01298701298701299</v>
+      </c>
+      <c r="AB33" s="4" t="n">
+        <v>-0.02361857698812531</v>
+      </c>
+      <c r="AC33" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>min_var</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_min_var</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="n">
+        <v>-0.01344322114561254</v>
+      </c>
+      <c r="I34" s="4" t="n">
+        <v>0.5678376799703716</v>
+      </c>
+      <c r="J34" s="3" t="n">
+        <v>-0.004658889614294975</v>
+      </c>
+      <c r="K34" s="4" t="n">
+        <v>0.2467532467532468</v>
+      </c>
+      <c r="L34" s="3" t="n">
+        <v>-0.004921191832077565</v>
+      </c>
+      <c r="M34" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="N34" s="3" t="n">
+        <v>-1.444163307681141</v>
+      </c>
+      <c r="O34" s="4" t="n">
+        <v>0.3816183816183816</v>
+      </c>
+      <c r="P34" s="3" t="n">
+        <v>0.06236261301228585</v>
+      </c>
+      <c r="Q34" s="4" t="n">
+        <v>0.2457542457542458</v>
+      </c>
+      <c r="R34" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="S34" s="4" t="n">
+        <v>0.9050949050949051</v>
+      </c>
+      <c r="T34" s="4" t="n">
+        <v>0.02302403815532553</v>
+      </c>
+      <c r="U34" s="4" t="n">
+        <v>0.5954045954045954</v>
+      </c>
+      <c r="V34" s="4" t="n">
+        <v>-0.009977682420035799</v>
+      </c>
+      <c r="W34" s="4" t="n">
+        <v>0.3066933066933067</v>
+      </c>
+      <c r="X34" s="3" t="n">
+        <v>0.0004084209794697705</v>
+      </c>
+      <c r="Y34" s="4" t="n">
+        <v>0.02797202797202797</v>
+      </c>
+      <c r="Z34" s="3" t="n">
+        <v>0.0007436449539777838</v>
+      </c>
+      <c r="AA34" s="4" t="n">
+        <v>0.002997002997002997</v>
+      </c>
+      <c r="AB34" s="4" t="n">
+        <v>-0.04209510316038856</v>
+      </c>
+      <c r="AC34" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward_changepoint_vix_cash</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="H35" s="4" t="n">
+        <v>0.01540307252726372</v>
+      </c>
+      <c r="I35" s="4" t="n">
+        <v>0.9162234449151502</v>
+      </c>
+      <c r="J35" s="3" t="n">
+        <v>-0.025925362189601</v>
+      </c>
+      <c r="K35" s="4" t="n">
+        <v>0.2497502497502498</v>
+      </c>
+      <c r="L35" s="3" t="n">
+        <v>-0.0654800624729398</v>
+      </c>
+      <c r="M35" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="N35" s="3" t="n">
+        <v>-5.769663384791662</v>
+      </c>
+      <c r="O35" s="4" t="n">
+        <v>0.4055944055944056</v>
+      </c>
+      <c r="P35" s="3" t="n">
+        <v>0.1749895058708758</v>
+      </c>
+      <c r="Q35" s="4" t="n">
+        <v>0.06893106893106893</v>
+      </c>
+      <c r="R35" s="2" t="n">
+        <v>239</v>
+      </c>
+      <c r="S35" s="4" t="n">
+        <v>0.7462537462537463</v>
+      </c>
+      <c r="T35" s="4" t="n">
+        <v>0.03034473622686903</v>
+      </c>
+      <c r="U35" s="4" t="n">
+        <v>0.7912087912087912</v>
+      </c>
+      <c r="V35" s="4" t="n">
+        <v>-0.07360026064613918</v>
+      </c>
+      <c r="W35" s="4" t="n">
+        <v>0.07392607392607392</v>
+      </c>
+      <c r="X35" s="3" t="n">
+        <v>0.007244822876207639</v>
+      </c>
+      <c r="Y35" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="Z35" s="3" t="n">
+        <v>0.008547177988475801</v>
+      </c>
+      <c r="AA35" s="4" t="n">
+        <v>0.001998001998001998</v>
+      </c>
+      <c r="AB35" s="4" t="n">
+        <v>-0.5087186424340846</v>
+      </c>
+      <c r="AC35" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>hmm</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>gspc</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward_hmm_gspc_cash</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="H36" s="4" t="n">
+        <v>-0.01798827095253898</v>
+      </c>
+      <c r="I36" s="4" t="n">
+        <v>0.8145349489948979</v>
+      </c>
+      <c r="J36" s="3" t="n">
+        <v>-0.01211246988699306</v>
+      </c>
+      <c r="K36" s="4" t="n">
+        <v>0.3906093906093906</v>
+      </c>
+      <c r="L36" s="3" t="n">
+        <v>-0.02156153382457399</v>
+      </c>
+      <c r="M36" s="4" t="n">
+        <v>0.02797202797202797</v>
+      </c>
+      <c r="N36" s="3" t="n">
+        <v>-3.159349281471714</v>
+      </c>
+      <c r="O36" s="4" t="n">
+        <v>0.4775224775224775</v>
+      </c>
+      <c r="P36" s="3" t="n">
+        <v>0.1269201431932957</v>
+      </c>
+      <c r="Q36" s="4" t="n">
+        <v>0.3156843156843157</v>
+      </c>
+      <c r="R36" s="2" t="n">
+        <v>-46</v>
+      </c>
+      <c r="S36" s="4" t="n">
+        <v>0.9090909090909091</v>
+      </c>
+      <c r="T36" s="4" t="n">
+        <v>0.03866000289883356</v>
+      </c>
+      <c r="U36" s="4" t="n">
+        <v>0.7112887112887113</v>
+      </c>
+      <c r="V36" s="4" t="n">
+        <v>-0.02854984054541138</v>
+      </c>
+      <c r="W36" s="4" t="n">
+        <v>0.4025974025974026</v>
+      </c>
+      <c r="X36" s="3" t="n">
+        <v>0.00149164309052963</v>
+      </c>
+      <c r="Y36" s="4" t="n">
+        <v>0.04195804195804196</v>
+      </c>
+      <c r="Z36" s="3" t="n">
+        <v>0.002648403711641878</v>
+      </c>
+      <c r="AA36" s="4" t="n">
+        <v>0.06893106893106893</v>
+      </c>
+      <c r="AB36" s="4" t="n">
+        <v>-0.1925005061617212</v>
+      </c>
+      <c r="AC36" s="4" t="n">
+        <v>0.003996003996003996</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_cash</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="H37" s="4" t="n">
+        <v>-0.05779916800058182</v>
+      </c>
+      <c r="I37" s="4" t="n">
+        <v>0.6464757764888456</v>
+      </c>
+      <c r="J37" s="3" t="n">
+        <v>-0.02894623575184743</v>
+      </c>
+      <c r="K37" s="4" t="n">
+        <v>0.1548451548451548</v>
+      </c>
+      <c r="L37" s="3" t="n">
+        <v>-0.05067358794004616</v>
+      </c>
+      <c r="M37" s="4" t="n">
+        <v>0.002997002997002997</v>
+      </c>
+      <c r="N37" s="3" t="n">
+        <v>-6.229309720114995</v>
+      </c>
+      <c r="O37" s="4" t="n">
+        <v>0.3176823176823177</v>
+      </c>
+      <c r="P37" s="3" t="n">
+        <v>0.1502054417833142</v>
+      </c>
+      <c r="Q37" s="4" t="n">
+        <v>0.1818181818181818</v>
+      </c>
+      <c r="R37" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="S37" s="4" t="n">
+        <v>0.919080919080919</v>
+      </c>
+      <c r="T37" s="4" t="n">
+        <v>0.002753101398576902</v>
+      </c>
+      <c r="U37" s="4" t="n">
+        <v>0.9730269730269731</v>
+      </c>
+      <c r="V37" s="4" t="n">
+        <v>-0.04047586964407746</v>
+      </c>
+      <c r="W37" s="4" t="n">
+        <v>0.2527472527472527</v>
+      </c>
+      <c r="X37" s="3" t="n">
+        <v>0.005013214393132409</v>
+      </c>
+      <c r="Y37" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="Z37" s="3" t="n">
+        <v>0.006288312952449481</v>
+      </c>
+      <c r="AA37" s="4" t="n">
+        <v>0.007992007992007992</v>
+      </c>
+      <c r="AB37" s="4" t="n">
+        <v>-0.413468439164499</v>
+      </c>
+      <c r="AC37" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>min_var</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward_changepoint_vix_min_var</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="H38" s="4" t="n">
+        <v>0.005446880511825907</v>
+      </c>
+      <c r="I38" s="4" t="n">
+        <v>0.8307095213721926</v>
+      </c>
+      <c r="J38" s="3" t="n">
+        <v>-0.001448157951621662</v>
+      </c>
+      <c r="K38" s="4" t="n">
+        <v>0.7592407592407593</v>
+      </c>
+      <c r="L38" s="3" t="n">
+        <v>-0.005699025034900579</v>
+      </c>
+      <c r="M38" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="N38" s="3" t="n">
+        <v>-0.4294681186205072</v>
+      </c>
+      <c r="O38" s="4" t="n">
+        <v>0.7642357642357642</v>
+      </c>
+      <c r="P38" s="3" t="n">
+        <v>0.06234945689994187</v>
+      </c>
+      <c r="Q38" s="4" t="n">
+        <v>0.1628371628371628</v>
+      </c>
+      <c r="R38" s="2" t="n">
+        <v>-111</v>
+      </c>
+      <c r="S38" s="4" t="n">
+        <v>0.4995004995004995</v>
+      </c>
+      <c r="T38" s="4" t="n">
+        <v>0.02712248103105272</v>
+      </c>
+      <c r="U38" s="4" t="n">
+        <v>0.3266733266733267</v>
+      </c>
+      <c r="V38" s="4" t="n">
+        <v>-0.01709431356475449</v>
+      </c>
+      <c r="W38" s="4" t="n">
+        <v>0.1428571428571428</v>
+      </c>
+      <c r="X38" s="3" t="n">
+        <v>0.0005087603800774162</v>
+      </c>
+      <c r="Y38" s="4" t="n">
+        <v>0.02197802197802198</v>
+      </c>
+      <c r="Z38" s="3" t="n">
+        <v>0.000810759043010284</v>
+      </c>
+      <c r="AA38" s="4" t="n">
+        <v>0.001998001998001998</v>
+      </c>
+      <c r="AB38" s="4" t="n">
+        <v>-0.04671290892586799</v>
+      </c>
+      <c r="AC38" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>hmm</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>gspc</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>min_var</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward_hmm_gspc_min_var</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="H39" s="4" t="n">
+        <v>-0.007190981962361068</v>
+      </c>
+      <c r="I39" s="4" t="n">
+        <v>0.6809623482125677</v>
+      </c>
+      <c r="J39" s="3" t="n">
+        <v>-0.00240692316010313</v>
+      </c>
+      <c r="K39" s="4" t="n">
+        <v>0.5314685314685315</v>
+      </c>
+      <c r="L39" s="3" t="n">
+        <v>-0.002524246772238781</v>
+      </c>
+      <c r="M39" s="4" t="n">
+        <v>0.01298701298701299</v>
+      </c>
+      <c r="N39" s="3" t="n">
+        <v>-0.705466740549145</v>
+      </c>
+      <c r="O39" s="4" t="n">
+        <v>0.5884115884115884</v>
+      </c>
+      <c r="P39" s="3" t="n">
+        <v>0.04456428819105318</v>
+      </c>
+      <c r="Q39" s="4" t="n">
+        <v>0.2747252747252747</v>
+      </c>
+      <c r="R39" s="2" t="n">
+        <v>-46</v>
+      </c>
+      <c r="S39" s="4" t="n">
+        <v>0.6843156843156843</v>
+      </c>
+      <c r="T39" s="4" t="n">
+        <v>0.01530510727009871</v>
+      </c>
+      <c r="U39" s="4" t="n">
+        <v>0.5234765234765235</v>
+      </c>
+      <c r="V39" s="4" t="n">
+        <v>-0.01174637353722166</v>
+      </c>
+      <c r="W39" s="4" t="n">
+        <v>0.2737262737262737</v>
+      </c>
+      <c r="X39" s="3" t="n">
+        <v>0.0001576880783605017</v>
+      </c>
+      <c r="Y39" s="4" t="n">
+        <v>0.2497502497502498</v>
+      </c>
+      <c r="Z39" s="3" t="n">
+        <v>0.0004048702384107858</v>
+      </c>
+      <c r="AA39" s="4" t="n">
+        <v>0.03396603396603397</v>
+      </c>
+      <c r="AB39" s="4" t="n">
+        <v>-0.02043650009262732</v>
+      </c>
+      <c r="AC39" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>min_var</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_min_var</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="H40" s="4" t="n">
+        <v>-0.00962126575179364</v>
+      </c>
+      <c r="I40" s="4" t="n">
+        <v>0.6844297954076739</v>
+      </c>
+      <c r="J40" s="3" t="n">
+        <v>-0.003662093641389363</v>
+      </c>
+      <c r="K40" s="4" t="n">
+        <v>0.3896103896103896</v>
+      </c>
+      <c r="L40" s="3" t="n">
+        <v>-0.004462729920455599</v>
+      </c>
+      <c r="M40" s="4" t="n">
+        <v>0.001998001998001998</v>
+      </c>
+      <c r="N40" s="3" t="n">
+        <v>-1.057042468027431</v>
+      </c>
+      <c r="O40" s="4" t="n">
+        <v>0.4755244755244755</v>
+      </c>
+      <c r="P40" s="3" t="n">
+        <v>0.06234945689994198</v>
+      </c>
+      <c r="Q40" s="4" t="n">
+        <v>0.2437562437562437</v>
+      </c>
+      <c r="R40" s="2" t="n">
+        <v>-40</v>
+      </c>
+      <c r="S40" s="4" t="n">
+        <v>0.7192807192807192</v>
+      </c>
+      <c r="T40" s="4" t="n">
+        <v>0.02162729678921779</v>
+      </c>
+      <c r="U40" s="4" t="n">
+        <v>0.5224775224775224</v>
+      </c>
+      <c r="V40" s="4" t="n">
+        <v>-0.01432913978152671</v>
+      </c>
+      <c r="W40" s="4" t="n">
+        <v>0.2577422577422577</v>
+      </c>
+      <c r="X40" s="3" t="n">
+        <v>0.0004115272945089642</v>
+      </c>
+      <c r="Y40" s="4" t="n">
+        <v>0.06793206793206794</v>
+      </c>
+      <c r="Z40" s="3" t="n">
+        <v>0.0007105613333237178</v>
+      </c>
+      <c r="AA40" s="4" t="n">
+        <v>0.005994005994005994</v>
+      </c>
+      <c r="AB40" s="4" t="n">
+        <v>-0.03824373831375161</v>
+      </c>
+      <c r="AC40" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>xgb</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>xgb_t_10_holdout_changepoint_vix_cash</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>xgb_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="H41" s="4" t="n">
+        <v>-0.1716822254948861</v>
+      </c>
+      <c r="I41" s="4" t="n">
+        <v>0.2538623035137922</v>
+      </c>
+      <c r="J41" s="3" t="n">
+        <v>-0.05790027712558324</v>
+      </c>
+      <c r="K41" s="4" t="n">
+        <v>0.06693306693306693</v>
+      </c>
+      <c r="L41" s="3" t="n">
+        <v>-0.08916910725384361</v>
+      </c>
+      <c r="M41" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="N41" s="3" t="n">
+        <v>-12.2741372067237</v>
+      </c>
+      <c r="O41" s="4" t="n">
+        <v>0.3106893106893107</v>
+      </c>
+      <c r="P41" s="3" t="n">
+        <v>0.1482624534486786</v>
+      </c>
+      <c r="Q41" s="4" t="n">
+        <v>0.2717282717282717</v>
+      </c>
+      <c r="R41" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="S41" s="4" t="n">
+        <v>0.9820179820179821</v>
+      </c>
+      <c r="T41" s="4" t="n">
+        <v>-0.07041856026962125</v>
+      </c>
+      <c r="U41" s="4" t="n">
+        <v>0.5454545454545454</v>
+      </c>
+      <c r="V41" s="4" t="n">
+        <v>-0.02130107702716516</v>
+      </c>
+      <c r="W41" s="4" t="n">
+        <v>0.7382617382617382</v>
+      </c>
+      <c r="X41" s="3" t="n">
+        <v>0.009687970369961166</v>
+      </c>
+      <c r="Y41" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="Z41" s="3" t="n">
+        <v>0.0118398586929121</v>
+      </c>
+      <c r="AA41" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="AB41" s="4" t="n">
+        <v>-0.6382044544207303</v>
+      </c>
+      <c r="AC41" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>xgb</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>hmm</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>gspc</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>xgb_t_10_holdout_hmm_gspc_cash</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>xgb_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="H42" s="4" t="n">
+        <v>-0.06197847848519501</v>
+      </c>
+      <c r="I42" s="4" t="n">
+        <v>0.6395604622582333</v>
+      </c>
+      <c r="J42" s="3" t="n">
+        <v>-0.03598456625666656</v>
+      </c>
+      <c r="K42" s="4" t="n">
+        <v>0.1488511488511489</v>
+      </c>
+      <c r="L42" s="3" t="n">
+        <v>-0.06643380081480038</v>
+      </c>
+      <c r="M42" s="4" t="n">
+        <v>0.002997002997002997</v>
+      </c>
+      <c r="N42" s="3" t="n">
+        <v>-9.526501145852549</v>
+      </c>
+      <c r="O42" s="4" t="n">
+        <v>0.3556443556443556</v>
+      </c>
+      <c r="P42" s="3" t="n">
+        <v>0.08517467615079055</v>
+      </c>
+      <c r="Q42" s="4" t="n">
+        <v>0.4935064935064935</v>
+      </c>
+      <c r="R42" s="2" t="n">
+        <v>1912</v>
+      </c>
+      <c r="S42" s="4" t="n">
+        <v>0.3526473526473526</v>
+      </c>
+      <c r="T42" s="4" t="n">
+        <v>-0.04077390609266565</v>
+      </c>
+      <c r="U42" s="4" t="n">
+        <v>0.6543456543456544</v>
+      </c>
+      <c r="V42" s="4" t="n">
+        <v>0.07011530462197743</v>
+      </c>
+      <c r="W42" s="4" t="n">
+        <v>0.5844155844155844</v>
+      </c>
+      <c r="X42" s="3" t="n">
+        <v>0.005590476981418114</v>
+      </c>
+      <c r="Y42" s="4" t="n">
+        <v>0.001998001998001998</v>
+      </c>
+      <c r="Z42" s="3" t="n">
+        <v>0.008902060313996516</v>
+      </c>
+      <c r="AA42" s="4" t="n">
+        <v>0.004995004995004995</v>
+      </c>
+      <c r="AB42" s="4" t="n">
+        <v>-0.5081293118274441</v>
+      </c>
+      <c r="AC42" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>xgb</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>xgb_t_10_holdout_wasserstein_gspc_vix_cash</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>xgb_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="H43" s="4" t="n">
+        <v>-0.02577140658841374</v>
+      </c>
+      <c r="I43" s="4" t="n">
+        <v>0.8763732273939775</v>
+      </c>
+      <c r="J43" s="3" t="n">
+        <v>-0.04372988185684751</v>
+      </c>
+      <c r="K43" s="4" t="n">
+        <v>0.1218781218781219</v>
+      </c>
+      <c r="L43" s="3" t="n">
+        <v>-0.1046509641511053</v>
+      </c>
+      <c r="M43" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="N43" s="3" t="n">
+        <v>-10.67645657084161</v>
+      </c>
+      <c r="O43" s="4" t="n">
+        <v>0.3536463536463537</v>
+      </c>
+      <c r="P43" s="3" t="n">
+        <v>0.35861622273174</v>
+      </c>
+      <c r="Q43" s="4" t="n">
+        <v>0.02697302697302697</v>
+      </c>
+      <c r="R43" s="2" t="n">
+        <v>-90</v>
+      </c>
+      <c r="S43" s="4" t="n">
+        <v>0.916083916083916</v>
+      </c>
+      <c r="T43" s="4" t="n">
+        <v>0.06489528042820231</v>
+      </c>
+      <c r="U43" s="4" t="n">
+        <v>0.6223776223776224</v>
+      </c>
+      <c r="V43" s="4" t="n">
+        <v>-0.06139479015647846</v>
+      </c>
+      <c r="W43" s="4" t="n">
+        <v>0.2837162837162837</v>
+      </c>
+      <c r="X43" s="3" t="n">
+        <v>0.009444731658412314</v>
+      </c>
+      <c r="Y43" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="Z43" s="3" t="n">
+        <v>0.01400772046794249</v>
+      </c>
+      <c r="AA43" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="AB43" s="4" t="n">
+        <v>-0.7310499809282438</v>
+      </c>
+      <c r="AC43" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>xgb</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>xgb_t_10_holdout_changepoint_vix_hrp</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>xgb_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="H44" s="4" t="n">
+        <v>0.02576689357967399</v>
+      </c>
+      <c r="I44" s="4" t="n">
+        <v>0.6221859475926292</v>
+      </c>
+      <c r="J44" s="3" t="n">
+        <v>-0.007643277148308827</v>
+      </c>
+      <c r="K44" s="4" t="n">
+        <v>0.5604395604395604</v>
+      </c>
+      <c r="L44" s="3" t="n">
+        <v>-0.03260653055795482</v>
+      </c>
+      <c r="M44" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="N44" s="3" t="n">
+        <v>-2.783922570969835</v>
+      </c>
+      <c r="O44" s="4" t="n">
+        <v>0.6273726273726273</v>
+      </c>
+      <c r="P44" s="3" t="n">
+        <v>0.1599778535892</v>
+      </c>
+      <c r="Q44" s="4" t="n">
+        <v>0.05094905094905095</v>
+      </c>
+      <c r="R44" s="2" t="n">
+        <v>179</v>
+      </c>
+      <c r="S44" s="4" t="n">
+        <v>0.7912087912087912</v>
+      </c>
+      <c r="T44" s="4" t="n">
+        <v>0.04236351178295267</v>
+      </c>
+      <c r="U44" s="4" t="n">
+        <v>0.3766233766233766</v>
+      </c>
+      <c r="V44" s="4" t="n">
+        <v>-0.0353274142970693</v>
+      </c>
+      <c r="W44" s="4" t="n">
+        <v>0.2047952047952048</v>
+      </c>
+      <c r="X44" s="3" t="n">
+        <v>0.003230525133207606</v>
+      </c>
+      <c r="Y44" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="Z44" s="3" t="n">
+        <v>0.004965257197532758</v>
+      </c>
+      <c r="AA44" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="AB44" s="4" t="n">
+        <v>-0.1537546728417496</v>
+      </c>
+      <c r="AC44" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>xgb</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>hmm</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>gspc</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>xgb_t_10_holdout_hmm_gspc_hrp</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>xgb_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="H45" s="4" t="n">
+        <v>0.02077716299045124</v>
+      </c>
+      <c r="I45" s="4" t="n">
+        <v>0.6243137386598594</v>
+      </c>
+      <c r="J45" s="3" t="n">
+        <v>-0.005460741450865961</v>
+      </c>
+      <c r="K45" s="4" t="n">
+        <v>0.6013986013986014</v>
+      </c>
+      <c r="L45" s="3" t="n">
+        <v>-0.02493773460988299</v>
+      </c>
+      <c r="M45" s="4" t="n">
+        <v>0.001998001998001998</v>
+      </c>
+      <c r="N45" s="3" t="n">
+        <v>-2.041426070479689</v>
+      </c>
+      <c r="O45" s="4" t="n">
+        <v>0.6693306693306693</v>
+      </c>
+      <c r="P45" s="3" t="n">
+        <v>0.1122438414854067</v>
+      </c>
+      <c r="Q45" s="4" t="n">
+        <v>0.06693306693306693</v>
+      </c>
+      <c r="R45" s="2" t="n">
+        <v>431</v>
+      </c>
+      <c r="S45" s="4" t="n">
+        <v>0.6663336663336663</v>
+      </c>
+      <c r="T45" s="4" t="n">
+        <v>0.02671068918435812</v>
+      </c>
+      <c r="U45" s="4" t="n">
+        <v>0.5264735264735265</v>
+      </c>
+      <c r="V45" s="4" t="n">
+        <v>0.000869546796925913</v>
+      </c>
+      <c r="W45" s="4" t="n">
+        <v>0.981018981018981</v>
+      </c>
+      <c r="X45" s="3" t="n">
+        <v>0.001944881680069711</v>
+      </c>
+      <c r="Y45" s="4" t="n">
+        <v>0.002997002997002997</v>
+      </c>
+      <c r="Z45" s="3" t="n">
+        <v>0.003930149976591153</v>
+      </c>
+      <c r="AA45" s="4" t="n">
+        <v>0.003996003996003996</v>
+      </c>
+      <c r="AB45" s="4" t="n">
+        <v>-0.1173858333721909</v>
+      </c>
+      <c r="AC45" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>xgb</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>xgb_t_10_holdout_wasserstein_gspc_vix_hrp</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>xgb_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="H46" s="4" t="n">
+        <v>0.03861333985080591</v>
+      </c>
+      <c r="I46" s="4" t="n">
+        <v>0.4364253179865193</v>
+      </c>
+      <c r="J46" s="3" t="n">
+        <v>-0.005654551751015049</v>
+      </c>
+      <c r="K46" s="4" t="n">
+        <v>0.6193806193806194</v>
+      </c>
+      <c r="L46" s="3" t="n">
+        <v>-0.03399622065898844</v>
+      </c>
+      <c r="M46" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="N46" s="3" t="n">
+        <v>-2.108981549261356</v>
+      </c>
+      <c r="O46" s="4" t="n">
+        <v>0.6783216783216783</v>
+      </c>
+      <c r="P46" s="3" t="n">
+        <v>0.1187164296567371</v>
+      </c>
+      <c r="Q46" s="4" t="n">
+        <v>0.03696303696303696</v>
+      </c>
+      <c r="R46" s="2" t="n">
+        <v>285</v>
+      </c>
+      <c r="S46" s="4" t="n">
+        <v>0.7522477522477522</v>
+      </c>
+      <c r="T46" s="4" t="n">
+        <v>0.02886245423380482</v>
+      </c>
+      <c r="U46" s="4" t="n">
+        <v>0.4805194805194805</v>
+      </c>
+      <c r="V46" s="4" t="n">
+        <v>-0.02075923206433672</v>
+      </c>
+      <c r="W46" s="4" t="n">
+        <v>0.4045954045954046</v>
+      </c>
+      <c r="X46" s="3" t="n">
+        <v>0.003140384640914234</v>
+      </c>
+      <c r="Y46" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="Z46" s="3" t="n">
+        <v>0.005428490004959666</v>
+      </c>
+      <c r="AA46" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="AB46" s="4" t="n">
+        <v>-0.1635472661897504</v>
+      </c>
+      <c r="AC46" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>xgb</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>xgb_t_10_holdout_changepoint_vix_cash</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>xgb_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="H47" s="4" t="n">
+        <v>-0.3014990404381687</v>
+      </c>
+      <c r="I47" s="4" t="n">
+        <v>0.03831142647153729</v>
+      </c>
+      <c r="J47" s="3" t="n">
+        <v>-0.08042028790585043</v>
+      </c>
+      <c r="K47" s="4" t="n">
+        <v>0.01498501498501499</v>
+      </c>
+      <c r="L47" s="3" t="n">
+        <v>-0.08486279193652446</v>
+      </c>
+      <c r="M47" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="N47" s="3" t="n">
+        <v>-19.0145963704081</v>
+      </c>
+      <c r="O47" s="4" t="n">
+        <v>0.2637362637362637</v>
+      </c>
+      <c r="P47" s="3" t="n">
+        <v>0.07701365480882871</v>
+      </c>
+      <c r="Q47" s="4" t="n">
+        <v>0.5304695304695305</v>
+      </c>
+      <c r="R47" s="2" t="n">
+        <v>-99</v>
+      </c>
+      <c r="S47" s="4" t="n">
+        <v>0.949050949050949</v>
+      </c>
+      <c r="T47" s="4" t="n">
+        <v>-0.1362801993020788</v>
+      </c>
+      <c r="U47" s="4" t="n">
+        <v>0.2427572427572428</v>
+      </c>
+      <c r="V47" s="4" t="n">
+        <v>0.007395396104199675</v>
+      </c>
+      <c r="W47" s="4" t="n">
+        <v>0.9110889110889111</v>
+      </c>
+      <c r="X47" s="3" t="n">
+        <v>0.009366530097647367</v>
+      </c>
+      <c r="Y47" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="Z47" s="3" t="n">
+        <v>0.01057514251902082</v>
+      </c>
+      <c r="AA47" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="AB47" s="4" t="n">
+        <v>-0.619078796929032</v>
+      </c>
+      <c r="AC47" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>xgb</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>hmm</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>gspc</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>xgb_t_10_holdout_hmm_gspc_cash</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>xgb_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="H48" s="4" t="n">
+        <v>-0.143409686335606</v>
+      </c>
+      <c r="I48" s="4" t="n">
+        <v>0.1810728980527664</v>
+      </c>
+      <c r="J48" s="3" t="n">
+        <v>-0.04825220780731969</v>
+      </c>
+      <c r="K48" s="4" t="n">
+        <v>0.04595404595404595</v>
+      </c>
+      <c r="L48" s="3" t="n">
+        <v>-0.04876937753254826</v>
+      </c>
+      <c r="M48" s="4" t="n">
+        <v>0.001998001998001998</v>
+      </c>
+      <c r="N48" s="3" t="n">
+        <v>-15.38743894540662</v>
+      </c>
+      <c r="O48" s="4" t="n">
+        <v>0.2717282717282717</v>
+      </c>
+      <c r="P48" s="3" t="n">
+        <v>-0.07752127685783605</v>
+      </c>
+      <c r="Q48" s="4" t="n">
+        <v>0.6223776223776224</v>
+      </c>
+      <c r="R48" s="2" t="n">
+        <v>2054</v>
+      </c>
+      <c r="S48" s="4" t="n">
+        <v>0.2467532467532468</v>
+      </c>
+      <c r="T48" s="4" t="n">
+        <v>-0.1037215345301765</v>
+      </c>
+      <c r="U48" s="4" t="n">
+        <v>0.2827172827172827</v>
+      </c>
+      <c r="V48" s="4" t="n">
+        <v>0.1048798670354054</v>
+      </c>
+      <c r="W48" s="4" t="n">
+        <v>0.3926073926073926</v>
+      </c>
+      <c r="X48" s="3" t="n">
+        <v>0.004341480976965247</v>
+      </c>
+      <c r="Y48" s="4" t="n">
+        <v>0.003996003996003996</v>
+      </c>
+      <c r="Z48" s="3" t="n">
+        <v>0.00597156754903342</v>
+      </c>
+      <c r="AA48" s="4" t="n">
+        <v>0.01298701298701299</v>
+      </c>
+      <c r="AB48" s="4" t="n">
+        <v>-0.386838025915495</v>
+      </c>
+      <c r="AC48" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>xgb</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>xgb_t_10_holdout_wasserstein_gspc_vix_cash</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>xgb_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="H49" s="4" t="n">
+        <v>-0.2436667802081738</v>
+      </c>
+      <c r="I49" s="4" t="n">
+        <v>0.1015858711584168</v>
+      </c>
+      <c r="J49" s="3" t="n">
+        <v>-0.07308290532395006</v>
+      </c>
+      <c r="K49" s="4" t="n">
+        <v>0.01198801198801199</v>
+      </c>
+      <c r="L49" s="3" t="n">
+        <v>-0.08851591119163327</v>
+      </c>
+      <c r="M49" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="N49" s="3" t="n">
+        <v>-18.42892748026928</v>
+      </c>
+      <c r="O49" s="4" t="n">
+        <v>0.2627372627372627</v>
+      </c>
+      <c r="P49" s="3" t="n">
+        <v>0.1207316783327719</v>
+      </c>
+      <c r="Q49" s="4" t="n">
+        <v>0.3236763236763237</v>
+      </c>
+      <c r="R49" s="2" t="n">
+        <v>1788</v>
+      </c>
+      <c r="S49" s="4" t="n">
+        <v>0.2677322677322677</v>
+      </c>
+      <c r="T49" s="4" t="n">
+        <v>-0.1111976851920207</v>
+      </c>
+      <c r="U49" s="4" t="n">
+        <v>0.3256743256743257</v>
+      </c>
+      <c r="V49" s="4" t="n">
+        <v>0.02845124435085414</v>
+      </c>
+      <c r="W49" s="4" t="n">
+        <v>0.7192807192807192</v>
+      </c>
+      <c r="X49" s="3" t="n">
+        <v>0.008847812160632035</v>
+      </c>
+      <c r="Y49" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="Z49" s="3" t="n">
+        <v>0.01124790742961709</v>
+      </c>
+      <c r="AA49" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="AB49" s="4" t="n">
+        <v>-0.6473041678876326</v>
+      </c>
+      <c r="AC49" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>xgb</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>xgb_t_10_holdout_changepoint_vix_hrp</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>xgb_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="H50" s="4" t="n">
+        <v>-0.03253118282915834</v>
+      </c>
+      <c r="I50" s="4" t="n">
+        <v>0.5343018052169557</v>
+      </c>
+      <c r="J50" s="3" t="n">
+        <v>-0.02071227286009046</v>
+      </c>
+      <c r="K50" s="4" t="n">
+        <v>0.1178821178821179</v>
+      </c>
+      <c r="L50" s="3" t="n">
+        <v>-0.03087241830004805</v>
+      </c>
+      <c r="M50" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="N50" s="3" t="n">
+        <v>-8.841930122132743</v>
+      </c>
+      <c r="O50" s="4" t="n">
+        <v>0.3486513486513487</v>
+      </c>
+      <c r="P50" s="3" t="n">
+        <v>0.1028262190106602</v>
+      </c>
+      <c r="Q50" s="4" t="n">
+        <v>0.07692307692307693</v>
+      </c>
+      <c r="R50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S50" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="T50" s="4" t="n">
+        <v>0.002656839015448109</v>
+      </c>
+      <c r="U50" s="4" t="n">
+        <v>0.9590409590409591</v>
+      </c>
+      <c r="V50" s="4" t="n">
+        <v>-0.01786931242067036</v>
+      </c>
+      <c r="W50" s="4" t="n">
+        <v>0.3106893106893107</v>
+      </c>
+      <c r="X50" s="3" t="n">
+        <v>0.003303539927914552</v>
+      </c>
+      <c r="Y50" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="Z50" s="3" t="n">
+        <v>0.00441538675371126</v>
+      </c>
+      <c r="AA50" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="AB50" s="4" t="n">
+        <v>-0.1474050163272989</v>
+      </c>
+      <c r="AC50" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>xgb</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>hmm</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>gspc</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>xgb_t_10_holdout_hmm_gspc_hrp</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>xgb_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="H51" s="4" t="n">
+        <v>-0.03138845571395249</v>
+      </c>
+      <c r="I51" s="4" t="n">
+        <v>0.4484164185676587</v>
+      </c>
+      <c r="J51" s="3" t="n">
+        <v>-0.01612368102755375</v>
+      </c>
+      <c r="K51" s="4" t="n">
+        <v>0.1358641358641359</v>
+      </c>
+      <c r="L51" s="3" t="n">
+        <v>-0.02039740607100404</v>
+      </c>
+      <c r="M51" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="N51" s="3" t="n">
+        <v>-7.249023744114284</v>
+      </c>
+      <c r="O51" s="4" t="n">
+        <v>0.3426573426573427</v>
+      </c>
+      <c r="P51" s="3" t="n">
+        <v>-0.001172430361388255</v>
+      </c>
+      <c r="Q51" s="4" t="n">
+        <v>0.977022977022977</v>
+      </c>
+      <c r="R51" s="2" t="n">
+        <v>1644</v>
+      </c>
+      <c r="S51" s="4" t="n">
+        <v>0.4575424575424575</v>
+      </c>
+      <c r="T51" s="4" t="n">
+        <v>-0.02987922328400736</v>
+      </c>
+      <c r="U51" s="4" t="n">
+        <v>0.4605394605394605</v>
+      </c>
+      <c r="V51" s="4" t="n">
+        <v>0.04583924473695511</v>
+      </c>
+      <c r="W51" s="4" t="n">
+        <v>0.6673326673326674</v>
+      </c>
+      <c r="X51" s="3" t="n">
+        <v>0.001719999476472882</v>
+      </c>
+      <c r="Y51" s="4" t="n">
+        <v>0.006993006993006993</v>
+      </c>
+      <c r="Z51" s="3" t="n">
+        <v>0.002946093815169356</v>
+      </c>
+      <c r="AA51" s="4" t="n">
+        <v>0.002997002997002997</v>
+      </c>
+      <c r="AB51" s="4" t="n">
+        <v>-0.09687802573636928</v>
+      </c>
+      <c r="AC51" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>xgb</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>xgb_t_10_holdout_wasserstein_gspc_vix_hrp</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>xgb_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="H52" s="4" t="n">
+        <v>-0.03361852015540711</v>
+      </c>
+      <c r="I52" s="4" t="n">
+        <v>0.5077276549407901</v>
+      </c>
+      <c r="J52" s="3" t="n">
+        <v>-0.02112765934111525</v>
+      </c>
+      <c r="K52" s="4" t="n">
+        <v>0.07692307692307693</v>
+      </c>
+      <c r="L52" s="3" t="n">
+        <v>-0.03134131099954435</v>
+      </c>
+      <c r="M52" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="N52" s="3" t="n">
+        <v>-8.977464339570369</v>
+      </c>
+      <c r="O52" s="4" t="n">
+        <v>0.3176823176823177</v>
+      </c>
+      <c r="P52" s="3" t="n">
+        <v>0.02093635544644123</v>
+      </c>
+      <c r="Q52" s="4" t="n">
+        <v>0.7112887112887113</v>
+      </c>
+      <c r="R52" s="2" t="n">
+        <v>158</v>
+      </c>
+      <c r="S52" s="4" t="n">
+        <v>0.6433566433566433</v>
+      </c>
+      <c r="T52" s="4" t="n">
+        <v>-0.03170014650179806</v>
+      </c>
+      <c r="U52" s="4" t="n">
+        <v>0.5014985014985015</v>
+      </c>
+      <c r="V52" s="4" t="n">
+        <v>0.01603652723851545</v>
+      </c>
+      <c r="W52" s="4" t="n">
+        <v>0.8251748251748252</v>
+      </c>
+      <c r="X52" s="3" t="n">
+        <v>0.003233446535503677</v>
+      </c>
+      <c r="Y52" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="Z52" s="3" t="n">
+        <v>0.004636796008445982</v>
+      </c>
+      <c r="AA52" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="AB52" s="4" t="n">
+        <v>-0.1511964679407871</v>
+      </c>
+      <c r="AC52" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>xgb</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>xgb_t_10_holdout_changepoint_vix_cash</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>xgb_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="H53" s="4" t="n">
+        <v>0.001506515237562462</v>
+      </c>
+      <c r="I53" s="4" t="n">
+        <v>0.991959017940474</v>
+      </c>
+      <c r="J53" s="3" t="n">
+        <v>-0.03765450996367931</v>
+      </c>
+      <c r="K53" s="4" t="n">
+        <v>0.2017982017982018</v>
+      </c>
+      <c r="L53" s="3" t="n">
+        <v>-0.0801574203054394</v>
+      </c>
+      <c r="M53" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="N53" s="3" t="n">
+        <v>-13.4232317725795</v>
+      </c>
+      <c r="O53" s="4" t="n">
+        <v>0.3906093906093906</v>
+      </c>
+      <c r="P53" s="3" t="n">
+        <v>0.2067102692785305</v>
+      </c>
+      <c r="Q53" s="4" t="n">
+        <v>0.04595404595404595</v>
+      </c>
+      <c r="R53" s="2" t="n">
+        <v>-1359</v>
+      </c>
+      <c r="S53" s="4" t="n">
+        <v>0.3796203796203796</v>
+      </c>
+      <c r="T53" s="4" t="n">
+        <v>0.02848026950294721</v>
+      </c>
+      <c r="U53" s="4" t="n">
+        <v>0.8301698301698301</v>
+      </c>
+      <c r="V53" s="4" t="n">
+        <v>-0.09187004267729318</v>
+      </c>
+      <c r="W53" s="4" t="n">
+        <v>0.06293706293706294</v>
+      </c>
+      <c r="X53" s="3" t="n">
+        <v>0.009554250961784624</v>
+      </c>
+      <c r="Y53" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="Z53" s="3" t="n">
+        <v>0.01013229390354213</v>
+      </c>
+      <c r="AA53" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="AB53" s="4" t="n">
+        <v>-0.6241584732339962</v>
+      </c>
+      <c r="AC53" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>xgb</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>hmm</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>gspc</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>xgb_t_10_holdout_hmm_gspc_cash</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>xgb_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="H54" s="4" t="n">
+        <v>-0.07084055846233754</v>
+      </c>
+      <c r="I54" s="4" t="n">
+        <v>0.3775586441030616</v>
+      </c>
+      <c r="J54" s="3" t="n">
+        <v>-0.02619967397689653</v>
+      </c>
+      <c r="K54" s="4" t="n">
+        <v>0.2017982017982018</v>
+      </c>
+      <c r="L54" s="3" t="n">
+        <v>-0.02518684355553741</v>
+      </c>
+      <c r="M54" s="4" t="n">
+        <v>0.01498501498501499</v>
+      </c>
+      <c r="N54" s="3" t="n">
+        <v>-10.55779782350935</v>
+      </c>
+      <c r="O54" s="4" t="n">
+        <v>0.3756243756243756</v>
+      </c>
+      <c r="P54" s="3" t="n">
+        <v>0.009242220543757673</v>
+      </c>
+      <c r="Q54" s="4" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="R54" s="2" t="n">
+        <v>-788</v>
+      </c>
+      <c r="S54" s="4" t="n">
+        <v>0.6593406593406593</v>
+      </c>
+      <c r="T54" s="4" t="n">
+        <v>-0.04741949374895432</v>
+      </c>
+      <c r="U54" s="4" t="n">
+        <v>0.5524475524475524</v>
+      </c>
+      <c r="V54" s="4" t="n">
+        <v>-0.01653106077511898</v>
+      </c>
+      <c r="W54" s="4" t="n">
+        <v>0.6063936063936064</v>
+      </c>
+      <c r="X54" s="3" t="n">
+        <v>0.001932547147389403</v>
+      </c>
+      <c r="Y54" s="4" t="n">
+        <v>0.03496503496503497</v>
+      </c>
+      <c r="Z54" s="3" t="n">
+        <v>0.002887158067750455</v>
+      </c>
+      <c r="AA54" s="4" t="n">
+        <v>0.04595404595404595</v>
+      </c>
+      <c r="AB54" s="4" t="n">
+        <v>-0.2319390927604771</v>
+      </c>
+      <c r="AC54" s="4" t="n">
+        <v>0.001998001998001998</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>xgb</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>xgb_t_10_holdout_wasserstein_gspc_vix_cash</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>xgb_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="H55" s="4" t="n">
+        <v>-0.1396815935529276</v>
+      </c>
+      <c r="I55" s="4" t="n">
+        <v>0.2762538172503837</v>
+      </c>
+      <c r="J55" s="3" t="n">
+        <v>-0.05074780440401451</v>
+      </c>
+      <c r="K55" s="4" t="n">
+        <v>0.06193806193806194</v>
+      </c>
+      <c r="L55" s="3" t="n">
+        <v>-0.06037608047221174</v>
+      </c>
+      <c r="M55" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="N55" s="3" t="n">
+        <v>-15.83616780413857</v>
+      </c>
+      <c r="O55" s="4" t="n">
+        <v>0.2817182817182817</v>
+      </c>
+      <c r="P55" s="3" t="n">
+        <v>0.04925419656447183</v>
+      </c>
+      <c r="Q55" s="4" t="n">
+        <v>0.5944055944055944</v>
+      </c>
+      <c r="R55" s="2" t="n">
+        <v>-18</v>
+      </c>
+      <c r="S55" s="4" t="n">
+        <v>0.975024975024975</v>
+      </c>
+      <c r="T55" s="4" t="n">
+        <v>-0.08463680442563051</v>
+      </c>
+      <c r="U55" s="4" t="n">
+        <v>0.4135864135864136</v>
+      </c>
+      <c r="V55" s="4" t="n">
+        <v>0.0009795485222206246</v>
+      </c>
+      <c r="W55" s="4" t="n">
+        <v>0.9820179820179821</v>
+      </c>
+      <c r="X55" s="3" t="n">
+        <v>0.005987233961079278</v>
+      </c>
+      <c r="Y55" s="4" t="n">
+        <v>0.001998001998001998</v>
+      </c>
+      <c r="Z55" s="3" t="n">
+        <v>0.007144989114456327</v>
+      </c>
+      <c r="AA55" s="4" t="n">
+        <v>0.003996003996003996</v>
+      </c>
+      <c r="AB55" s="4" t="n">
+        <v>-0.5026953020779104</v>
+      </c>
+      <c r="AC55" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>xgb</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>xgb_t_10_holdout_changepoint_vix_hrp</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>xgb_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="H56" s="4" t="n">
+        <v>-0.005480652935762717</v>
+      </c>
+      <c r="I56" s="4" t="n">
+        <v>0.9049101192966362</v>
+      </c>
+      <c r="J56" s="3" t="n">
+        <v>-0.01159377189409351</v>
+      </c>
+      <c r="K56" s="4" t="n">
+        <v>0.2977022977022977</v>
+      </c>
+      <c r="L56" s="3" t="n">
+        <v>-0.02189684052451077</v>
+      </c>
+      <c r="M56" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="N56" s="3" t="n">
+        <v>-5.507665377765001</v>
+      </c>
+      <c r="O56" s="4" t="n">
+        <v>0.4515484515484515</v>
+      </c>
+      <c r="P56" s="3" t="n">
+        <v>0.04869465173292375</v>
+      </c>
+      <c r="Q56" s="4" t="n">
+        <v>0.1338661338661339</v>
+      </c>
+      <c r="R56" s="2" t="n">
+        <v>-1337</v>
+      </c>
+      <c r="S56" s="4" t="n">
+        <v>0.3786213786213786</v>
+      </c>
+      <c r="T56" s="4" t="n">
+        <v>-0.001355038856039714</v>
+      </c>
+      <c r="U56" s="4" t="n">
+        <v>0.9660339660339661</v>
+      </c>
+      <c r="V56" s="4" t="n">
+        <v>-0.02744375878349598</v>
+      </c>
+      <c r="W56" s="4" t="n">
+        <v>0.08591408591408592</v>
+      </c>
+      <c r="X56" s="3" t="n">
+        <v>0.002631562740138656</v>
+      </c>
+      <c r="Y56" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="Z56" s="3" t="n">
+        <v>0.003025654609065235</v>
+      </c>
+      <c r="AA56" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="AB56" s="4" t="n">
+        <v>-0.1154270285651451</v>
+      </c>
+      <c r="AC56" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>xgb</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>hmm</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>gspc</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>xgb_t_10_holdout_hmm_gspc_hrp</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>xgb_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="H57" s="4" t="n">
+        <v>-0.0483562516317572</v>
+      </c>
+      <c r="I57" s="4" t="n">
+        <v>0.1149530297538403</v>
+      </c>
+      <c r="J57" s="3" t="n">
+        <v>-0.01410594034862976</v>
+      </c>
+      <c r="K57" s="4" t="n">
+        <v>0.1098901098901099</v>
+      </c>
+      <c r="L57" s="3" t="n">
+        <v>-0.007033623065330841</v>
+      </c>
+      <c r="M57" s="4" t="n">
+        <v>0.001998001998001998</v>
+      </c>
+      <c r="N57" s="3" t="n">
+        <v>-6.509830610993426</v>
+      </c>
+      <c r="O57" s="4" t="n">
+        <v>0.3056943056943057</v>
+      </c>
+      <c r="P57" s="3" t="n">
+        <v>0.009242220543757673</v>
+      </c>
+      <c r="Q57" s="4" t="n">
+        <v>0.6383616383616384</v>
+      </c>
+      <c r="R57" s="2" t="n">
+        <v>-46</v>
+      </c>
+      <c r="S57" s="4" t="n">
+        <v>0.7952047952047953</v>
+      </c>
+      <c r="T57" s="4" t="n">
+        <v>-0.02364328163895982</v>
+      </c>
+      <c r="U57" s="4" t="n">
+        <v>0.3386613386613387</v>
+      </c>
+      <c r="V57" s="4" t="n">
+        <v>-0.0057901662262628</v>
+      </c>
+      <c r="W57" s="4" t="n">
+        <v>0.4895104895104895</v>
+      </c>
+      <c r="X57" s="3" t="n">
+        <v>0.0005687627790352291</v>
+      </c>
+      <c r="Y57" s="4" t="n">
+        <v>0.1158841158841159</v>
+      </c>
+      <c r="Z57" s="3" t="n">
+        <v>0.0008427384746546515</v>
+      </c>
+      <c r="AA57" s="4" t="n">
+        <v>0.003996003996003996</v>
+      </c>
+      <c r="AB57" s="4" t="n">
+        <v>-0.03946237210000358</v>
+      </c>
+      <c r="AC57" s="4" t="n">
+        <v>0.002997002997002997</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>xgb</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>xgb_t_10_holdout_wasserstein_gspc_vix_hrp</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>xgb_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="H58" s="4" t="n">
+        <v>-0.06682770488576437</v>
+      </c>
+      <c r="I58" s="4" t="n">
+        <v>0.09606711341918887</v>
+      </c>
+      <c r="J58" s="3" t="n">
+        <v>-0.02192636084452486</v>
+      </c>
+      <c r="K58" s="4" t="n">
+        <v>0.03296703296703297</v>
+      </c>
+      <c r="L58" s="3" t="n">
+        <v>-0.0164367718740836</v>
+      </c>
+      <c r="M58" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="N58" s="3" t="n">
+        <v>-9.262741709241782</v>
+      </c>
+      <c r="O58" s="4" t="n">
+        <v>0.2647352647352647</v>
+      </c>
+      <c r="P58" s="3" t="n">
+        <v>0.005815568810700222</v>
+      </c>
+      <c r="Q58" s="4" t="n">
+        <v>0.8561438561438561</v>
+      </c>
+      <c r="R58" s="2" t="n">
+        <v>146</v>
+      </c>
+      <c r="S58" s="4" t="n">
+        <v>0.5924075924075924</v>
+      </c>
+      <c r="T58" s="4" t="n">
+        <v>-0.04026295140520977</v>
+      </c>
+      <c r="U58" s="4" t="n">
+        <v>0.2097902097902098</v>
+      </c>
+      <c r="V58" s="4" t="n">
+        <v>0.01546942800000328</v>
+      </c>
+      <c r="W58" s="4" t="n">
+        <v>0.7732267732267732</v>
+      </c>
+      <c r="X58" s="3" t="n">
+        <v>0.001952888341499832</v>
+      </c>
+      <c r="Y58" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="Z58" s="3" t="n">
+        <v>0.00238951969813091</v>
+      </c>
+      <c r="AA58" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="AB58" s="4" t="n">
+        <v>-0.08924351239431716</v>
+      </c>
+      <c r="AC58" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>rf</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout_changepoint_vix_cash</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="H59" s="4" t="n">
+        <v>-0.1726752531190568</v>
+      </c>
+      <c r="I59" s="4" t="n">
+        <v>0.2474348197231949</v>
+      </c>
+      <c r="J59" s="3" t="n">
+        <v>-0.05860014196201596</v>
+      </c>
+      <c r="K59" s="4" t="n">
+        <v>0.06193806193806194</v>
+      </c>
+      <c r="L59" s="3" t="n">
+        <v>-0.08857125983343905</v>
+      </c>
+      <c r="M59" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="N59" s="3" t="n">
+        <v>-12.77286791474006</v>
+      </c>
+      <c r="O59" s="4" t="n">
+        <v>0.3096903096903097</v>
+      </c>
+      <c r="P59" s="3" t="n">
+        <v>0.1264602791479713</v>
+      </c>
+      <c r="Q59" s="4" t="n">
+        <v>0.3416583416583416</v>
+      </c>
+      <c r="R59" s="2" t="n">
+        <v>-131</v>
+      </c>
+      <c r="S59" s="4" t="n">
+        <v>0.9040959040959041</v>
+      </c>
+      <c r="T59" s="4" t="n">
+        <v>-0.07611622964110387</v>
+      </c>
+      <c r="U59" s="4" t="n">
+        <v>0.5054945054945055</v>
+      </c>
+      <c r="V59" s="4" t="n">
+        <v>-0.02011497782873456</v>
+      </c>
+      <c r="W59" s="4" t="n">
+        <v>0.7542457542457542</v>
+      </c>
+      <c r="X59" s="3" t="n">
+        <v>0.009780522566476324</v>
+      </c>
+      <c r="Y59" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="Z59" s="3" t="n">
+        <v>0.01175588046894466</v>
+      </c>
+      <c r="AA59" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="AB59" s="4" t="n">
+        <v>-0.6440792472770288</v>
+      </c>
+      <c r="AC59" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>rf</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>hmm</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>gspc</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout_hmm_gspc_cash</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="H60" s="4" t="n">
+        <v>-0.05292669528901148</v>
+      </c>
+      <c r="I60" s="4" t="n">
+        <v>0.6896183548927676</v>
+      </c>
+      <c r="J60" s="3" t="n">
+        <v>-0.03507468967073148</v>
+      </c>
+      <c r="K60" s="4" t="n">
+        <v>0.1518481518481518</v>
+      </c>
+      <c r="L60" s="3" t="n">
+        <v>-0.06721563581056619</v>
+      </c>
+      <c r="M60" s="4" t="n">
+        <v>0.002997002997002997</v>
+      </c>
+      <c r="N60" s="3" t="n">
+        <v>-9.703405692722741</v>
+      </c>
+      <c r="O60" s="4" t="n">
+        <v>0.3686313686313686</v>
+      </c>
+      <c r="P60" s="3" t="n">
+        <v>0.0724433397725488</v>
+      </c>
+      <c r="Q60" s="4" t="n">
+        <v>0.5664335664335665</v>
+      </c>
+      <c r="R60" s="2" t="n">
+        <v>1676</v>
+      </c>
+      <c r="S60" s="4" t="n">
+        <v>0.3626373626373626</v>
+      </c>
+      <c r="T60" s="4" t="n">
+        <v>-0.04202230716520935</v>
+      </c>
+      <c r="U60" s="4" t="n">
+        <v>0.6473526473526473</v>
+      </c>
+      <c r="V60" s="4" t="n">
+        <v>0.06378442006684387</v>
+      </c>
+      <c r="W60" s="4" t="n">
+        <v>0.5994005994005994</v>
+      </c>
+      <c r="X60" s="3" t="n">
+        <v>0.005845235136465097</v>
+      </c>
+      <c r="Y60" s="4" t="n">
+        <v>0.001998001998001998</v>
+      </c>
+      <c r="Z60" s="3" t="n">
+        <v>0.009031936791739723</v>
+      </c>
+      <c r="AA60" s="4" t="n">
+        <v>0.004995004995004995</v>
+      </c>
+      <c r="AB60" s="4" t="n">
+        <v>-0.5165386039826418</v>
+      </c>
+      <c r="AC60" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>rf</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout_wasserstein_gspc_vix_cash</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="H61" s="4" t="n">
+        <v>-0.01316914477488927</v>
+      </c>
+      <c r="I61" s="4" t="n">
+        <v>0.936522680616664</v>
+      </c>
+      <c r="J61" s="3" t="n">
+        <v>-0.04282208798611047</v>
+      </c>
+      <c r="K61" s="4" t="n">
+        <v>0.1248751248751249</v>
+      </c>
+      <c r="L61" s="3" t="n">
+        <v>-0.1056330899378902</v>
+      </c>
+      <c r="M61" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="N61" s="3" t="n">
+        <v>-10.92246863937726</v>
+      </c>
+      <c r="O61" s="4" t="n">
+        <v>0.3596403596403596</v>
+      </c>
+      <c r="P61" s="3" t="n">
+        <v>0.3511735934955144</v>
+      </c>
+      <c r="Q61" s="4" t="n">
+        <v>0.02497502497502498</v>
+      </c>
+      <c r="R61" s="2" t="n">
+        <v>-247</v>
+      </c>
+      <c r="S61" s="4" t="n">
+        <v>0.7732267732267732</v>
+      </c>
+      <c r="T61" s="4" t="n">
+        <v>0.06839033544959655</v>
+      </c>
+      <c r="U61" s="4" t="n">
+        <v>0.5874125874125874</v>
+      </c>
+      <c r="V61" s="4" t="n">
+        <v>-0.06571499970943186</v>
+      </c>
+      <c r="W61" s="4" t="n">
+        <v>0.2397602397602398</v>
+      </c>
+      <c r="X61" s="3" t="n">
+        <v>0.009646193776317894</v>
+      </c>
+      <c r="Y61" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="Z61" s="3" t="n">
+        <v>0.01415382636994108</v>
+      </c>
+      <c r="AA61" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="AB61" s="4" t="n">
+        <v>-0.7421435029805363</v>
+      </c>
+      <c r="AC61" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>rf</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout_changepoint_vix_hrp</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="H62" s="4" t="n">
+        <v>0.02324080711198001</v>
+      </c>
+      <c r="I62" s="4" t="n">
+        <v>0.6642452664673189</v>
+      </c>
+      <c r="J62" s="3" t="n">
+        <v>-0.008310838851380911</v>
+      </c>
+      <c r="K62" s="4" t="n">
+        <v>0.5284715284715285</v>
+      </c>
+      <c r="L62" s="3" t="n">
+        <v>-0.03301959928954637</v>
+      </c>
+      <c r="M62" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="N62" s="3" t="n">
+        <v>-3.106973988692229</v>
+      </c>
+      <c r="O62" s="4" t="n">
+        <v>0.6103896103896104</v>
+      </c>
+      <c r="P62" s="3" t="n">
+        <v>0.1542026855020534</v>
+      </c>
+      <c r="Q62" s="4" t="n">
+        <v>0.05494505494505494</v>
+      </c>
+      <c r="R62" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="S62" s="4" t="n">
+        <v>0.949050949050949</v>
+      </c>
+      <c r="T62" s="4" t="n">
+        <v>0.0400734106238837</v>
+      </c>
+      <c r="U62" s="4" t="n">
+        <v>0.4135864135864136</v>
+      </c>
+      <c r="V62" s="4" t="n">
+        <v>-0.0388746395280981</v>
+      </c>
+      <c r="W62" s="4" t="n">
+        <v>0.1608391608391608</v>
+      </c>
+      <c r="X62" s="3" t="n">
+        <v>0.003488968799356989</v>
+      </c>
+      <c r="Y62" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="Z62" s="3" t="n">
+        <v>0.004955375618437712</v>
+      </c>
+      <c r="AA62" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="AB62" s="4" t="n">
+        <v>-0.1596217128200366</v>
+      </c>
+      <c r="AC62" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>rf</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>hmm</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>gspc</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout_hmm_gspc_hrp</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="H63" s="4" t="n">
+        <v>0.02753624524580801</v>
+      </c>
+      <c r="I63" s="4" t="n">
+        <v>0.5240385118348467</v>
+      </c>
+      <c r="J63" s="3" t="n">
+        <v>-0.004504641835546427</v>
+      </c>
+      <c r="K63" s="4" t="n">
+        <v>0.6763236763236763</v>
+      </c>
+      <c r="L63" s="3" t="n">
+        <v>-0.02614036647859141</v>
+      </c>
+      <c r="M63" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="N63" s="3" t="n">
+        <v>-1.762192354372106</v>
+      </c>
+      <c r="O63" s="4" t="n">
+        <v>0.7112887112887113</v>
+      </c>
+      <c r="P63" s="3" t="n">
+        <v>0.1057730119128827</v>
+      </c>
+      <c r="Q63" s="4" t="n">
+        <v>0.05894105894105894</v>
+      </c>
+      <c r="R63" s="2" t="n">
+        <v>218</v>
+      </c>
+      <c r="S63" s="4" t="n">
+        <v>0.7132867132867133</v>
+      </c>
+      <c r="T63" s="4" t="n">
+        <v>0.02721967966428257</v>
+      </c>
+      <c r="U63" s="4" t="n">
+        <v>0.4875124875124875</v>
+      </c>
+      <c r="V63" s="4" t="n">
+        <v>-0.00025823199367217</v>
+      </c>
+      <c r="W63" s="4" t="n">
+        <v>0.993006993006993</v>
+      </c>
+      <c r="X63" s="3" t="n">
+        <v>0.002044440582840777</v>
+      </c>
+      <c r="Y63" s="4" t="n">
+        <v>0.002997002997002997</v>
+      </c>
+      <c r="Z63" s="3" t="n">
+        <v>0.004137836798622795</v>
+      </c>
+      <c r="AA63" s="4" t="n">
+        <v>0.002997002997002997</v>
+      </c>
+      <c r="AB63" s="4" t="n">
+        <v>-0.1257931846943036</v>
+      </c>
+      <c r="AC63" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>rf</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout_wasserstein_gspc_vix_hrp</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="H64" s="4" t="n">
+        <v>0.04647709526915817</v>
+      </c>
+      <c r="I64" s="4" t="n">
+        <v>0.3629693816027645</v>
+      </c>
+      <c r="J64" s="3" t="n">
+        <v>-0.004729569635656239</v>
+      </c>
+      <c r="K64" s="4" t="n">
+        <v>0.6773226773226774</v>
+      </c>
+      <c r="L64" s="3" t="n">
+        <v>-0.03565862504283293</v>
+      </c>
+      <c r="M64" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="N64" s="3" t="n">
+        <v>-1.845198031218217</v>
+      </c>
+      <c r="O64" s="4" t="n">
+        <v>0.7132867132867133</v>
+      </c>
+      <c r="P64" s="3" t="n">
+        <v>0.1089322244498484</v>
+      </c>
+      <c r="Q64" s="4" t="n">
+        <v>0.03396603396603397</v>
+      </c>
+      <c r="R64" s="2" t="n">
+        <v>110</v>
+      </c>
+      <c r="S64" s="4" t="n">
+        <v>0.8101898101898102</v>
+      </c>
+      <c r="T64" s="4" t="n">
+        <v>0.02802903544840146</v>
+      </c>
+      <c r="U64" s="4" t="n">
+        <v>0.4725274725274725</v>
+      </c>
+      <c r="V64" s="4" t="n">
+        <v>-0.02288009171306227</v>
+      </c>
+      <c r="W64" s="4" t="n">
+        <v>0.3496503496503496</v>
+      </c>
+      <c r="X64" s="3" t="n">
+        <v>0.003322521695811369</v>
+      </c>
+      <c r="Y64" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="Z64" s="3" t="n">
+        <v>0.00566121582658689</v>
+      </c>
+      <c r="AA64" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="AB64" s="4" t="n">
+        <v>-0.1746489165907217</v>
+      </c>
+      <c r="AC64" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>rf</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout_changepoint_vix_cash</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="H65" s="4" t="n">
+        <v>-0.2849936764273014</v>
+      </c>
+      <c r="I65" s="4" t="n">
+        <v>0.05101416544884649</v>
+      </c>
+      <c r="J65" s="3" t="n">
+        <v>-0.07609534598844703</v>
+      </c>
+      <c r="K65" s="4" t="n">
+        <v>0.02197802197802198</v>
+      </c>
+      <c r="L65" s="3" t="n">
+        <v>-0.08609579237773024</v>
+      </c>
+      <c r="M65" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="N65" s="3" t="n">
+        <v>-16.11328215960244</v>
+      </c>
+      <c r="O65" s="4" t="n">
+        <v>0.2757242757242757</v>
+      </c>
+      <c r="P65" s="3" t="n">
+        <v>0.09082275934427086</v>
+      </c>
+      <c r="Q65" s="4" t="n">
+        <v>0.4905094905094905</v>
+      </c>
+      <c r="R65" s="2" t="n">
+        <v>-73</v>
+      </c>
+      <c r="S65" s="4" t="n">
+        <v>0.9570429570429571</v>
+      </c>
+      <c r="T65" s="4" t="n">
+        <v>-0.123260566999713</v>
+      </c>
+      <c r="U65" s="4" t="n">
+        <v>0.2717282717282717</v>
+      </c>
+      <c r="V65" s="4" t="n">
+        <v>-0.003727554509756537</v>
+      </c>
+      <c r="W65" s="4" t="n">
+        <v>0.954045954045954</v>
+      </c>
+      <c r="X65" s="3" t="n">
+        <v>0.009654571758843728</v>
+      </c>
+      <c r="Y65" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="Z65" s="3" t="n">
+        <v>0.01080011058373236</v>
+      </c>
+      <c r="AA65" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="AB65" s="4" t="n">
+        <v>-0.6289799387412144</v>
+      </c>
+      <c r="AC65" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>rf</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>hmm</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>gspc</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout_hmm_gspc_cash</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="H66" s="4" t="n">
+        <v>-0.1332423885916653</v>
+      </c>
+      <c r="I66" s="4" t="n">
+        <v>0.2208562677690253</v>
+      </c>
+      <c r="J66" s="3" t="n">
+        <v>-0.04540993013269837</v>
+      </c>
+      <c r="K66" s="4" t="n">
+        <v>0.06993006993006994</v>
+      </c>
+      <c r="L66" s="3" t="n">
+        <v>-0.05018815097646182</v>
+      </c>
+      <c r="M66" s="4" t="n">
+        <v>0.002997002997002997</v>
+      </c>
+      <c r="N66" s="3" t="n">
+        <v>-12.8658279654994</v>
+      </c>
+      <c r="O66" s="4" t="n">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="P66" s="3" t="n">
+        <v>-0.07140717675013097</v>
+      </c>
+      <c r="Q66" s="4" t="n">
+        <v>0.6523476523476524</v>
+      </c>
+      <c r="R66" s="2" t="n">
+        <v>2510</v>
+      </c>
+      <c r="S66" s="4" t="n">
+        <v>0.2647352647352647</v>
+      </c>
+      <c r="T66" s="4" t="n">
+        <v>-0.09350432143911658</v>
+      </c>
+      <c r="U66" s="4" t="n">
+        <v>0.3206793206793207</v>
+      </c>
+      <c r="V66" s="4" t="n">
+        <v>0.1064833356013841</v>
+      </c>
+      <c r="W66" s="4" t="n">
+        <v>0.4285714285714285</v>
+      </c>
+      <c r="X66" s="3" t="n">
+        <v>0.004699346324617392</v>
+      </c>
+      <c r="Y66" s="4" t="n">
+        <v>0.003996003996003996</v>
+      </c>
+      <c r="Z66" s="3" t="n">
+        <v>0.006234235244652435</v>
+      </c>
+      <c r="AA66" s="4" t="n">
+        <v>0.01398601398601399</v>
+      </c>
+      <c r="AB66" s="4" t="n">
+        <v>-0.3952056434913773</v>
+      </c>
+      <c r="AC66" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>rf</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout_wasserstein_gspc_vix_cash</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="H67" s="4" t="n">
+        <v>-0.2441430747473869</v>
+      </c>
+      <c r="I67" s="4" t="n">
+        <v>0.1012229795110997</v>
+      </c>
+      <c r="J67" s="3" t="n">
+        <v>-0.0709217072223178</v>
+      </c>
+      <c r="K67" s="4" t="n">
+        <v>0.01598401598401598</v>
+      </c>
+      <c r="L67" s="3" t="n">
+        <v>-0.08969946791518321</v>
+      </c>
+      <c r="M67" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="N67" s="3" t="n">
+        <v>-15.72877377607614</v>
+      </c>
+      <c r="O67" s="4" t="n">
+        <v>0.2687312687312687</v>
+      </c>
+      <c r="P67" s="3" t="n">
+        <v>0.1243953076158071</v>
+      </c>
+      <c r="Q67" s="4" t="n">
+        <v>0.3406593406593407</v>
+      </c>
+      <c r="R67" s="2" t="n">
+        <v>1804</v>
+      </c>
+      <c r="S67" s="4" t="n">
+        <v>0.2747252747252747</v>
+      </c>
+      <c r="T67" s="4" t="n">
+        <v>-0.1059384376852522</v>
+      </c>
+      <c r="U67" s="4" t="n">
+        <v>0.3326673326673327</v>
+      </c>
+      <c r="V67" s="4" t="n">
+        <v>0.02899984963161989</v>
+      </c>
+      <c r="W67" s="4" t="n">
+        <v>0.7312687312687313</v>
+      </c>
+      <c r="X67" s="3" t="n">
+        <v>0.009232030887728193</v>
+      </c>
+      <c r="Y67" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="Z67" s="3" t="n">
+        <v>0.01147993728699245</v>
+      </c>
+      <c r="AA67" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="AB67" s="4" t="n">
+        <v>-0.6570856367121546</v>
+      </c>
+      <c r="AC67" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>rf</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout_changepoint_vix_hrp</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="H68" s="4" t="n">
+        <v>-0.01373199356360233</v>
+      </c>
+      <c r="I68" s="4" t="n">
+        <v>0.7978528682021551</v>
+      </c>
+      <c r="J68" s="3" t="n">
+        <v>-0.01649480354975066</v>
+      </c>
+      <c r="K68" s="4" t="n">
+        <v>0.2277722277722278</v>
+      </c>
+      <c r="L68" s="3" t="n">
+        <v>-0.03256770027353886</v>
+      </c>
+      <c r="M68" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="N68" s="3" t="n">
+        <v>-6.385448314207768</v>
+      </c>
+      <c r="O68" s="4" t="n">
+        <v>0.4215784215784216</v>
+      </c>
+      <c r="P68" s="3" t="n">
+        <v>0.1198523679256871</v>
+      </c>
+      <c r="Q68" s="4" t="n">
+        <v>0.06593406593406594</v>
+      </c>
+      <c r="R68" s="2" t="n">
+        <v>-36</v>
+      </c>
+      <c r="S68" s="4" t="n">
+        <v>0.8411588411588412</v>
+      </c>
+      <c r="T68" s="4" t="n">
+        <v>0.01572869834838034</v>
+      </c>
+      <c r="U68" s="4" t="n">
+        <v>0.7042957042957043</v>
+      </c>
+      <c r="V68" s="4" t="n">
+        <v>-0.02897720615995911</v>
+      </c>
+      <c r="W68" s="4" t="n">
+        <v>0.2017982017982018</v>
+      </c>
+      <c r="X68" s="3" t="n">
+        <v>0.0038523489316073</v>
+      </c>
+      <c r="Y68" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="Z68" s="3" t="n">
+        <v>0.004712072563893301</v>
+      </c>
+      <c r="AA68" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="AB68" s="4" t="n">
+        <v>-0.1573035515575527</v>
+      </c>
+      <c r="AC68" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>rf</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>hmm</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>gspc</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout_hmm_gspc_hrp</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="H69" s="4" t="n">
+        <v>-0.01891712557672253</v>
+      </c>
+      <c r="I69" s="4" t="n">
+        <v>0.659685268926421</v>
+      </c>
+      <c r="J69" s="3" t="n">
+        <v>-0.013384432939631</v>
+      </c>
+      <c r="K69" s="4" t="n">
+        <v>0.2227772227772228</v>
+      </c>
+      <c r="L69" s="3" t="n">
+        <v>-0.0220193203962164</v>
+      </c>
+      <c r="M69" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="N69" s="3" t="n">
+        <v>-5.369986534361463</v>
+      </c>
+      <c r="O69" s="4" t="n">
+        <v>0.4085914085914086</v>
+      </c>
+      <c r="P69" s="3" t="n">
+        <v>0.004453090970216955</v>
+      </c>
+      <c r="Q69" s="4" t="n">
+        <v>0.9400599400599401</v>
+      </c>
+      <c r="R69" s="2" t="n">
+        <v>1611</v>
+      </c>
+      <c r="S69" s="4" t="n">
+        <v>0.5024975024975025</v>
+      </c>
+      <c r="T69" s="4" t="n">
+        <v>-0.02236768872400033</v>
+      </c>
+      <c r="U69" s="4" t="n">
+        <v>0.6133866133866134</v>
+      </c>
+      <c r="V69" s="4" t="n">
+        <v>0.04712532136492384</v>
+      </c>
+      <c r="W69" s="4" t="n">
+        <v>0.7232767232767233</v>
+      </c>
+      <c r="X69" s="3" t="n">
+        <v>0.002079222544581136</v>
+      </c>
+      <c r="Y69" s="4" t="n">
+        <v>0.001998001998001998</v>
+      </c>
+      <c r="Z69" s="3" t="n">
+        <v>0.003279934840986647</v>
+      </c>
+      <c r="AA69" s="4" t="n">
+        <v>0.002997002997002997</v>
+      </c>
+      <c r="AB69" s="4" t="n">
+        <v>-0.1052473211503661</v>
+      </c>
+      <c r="AC69" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>rf</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout_wasserstein_gspc_vix_hrp</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="H70" s="4" t="n">
+        <v>-0.02590160816235637</v>
+      </c>
+      <c r="I70" s="4" t="n">
+        <v>0.6190232276778218</v>
+      </c>
+      <c r="J70" s="3" t="n">
+        <v>-0.01916950552398725</v>
+      </c>
+      <c r="K70" s="4" t="n">
+        <v>0.1198801198801199</v>
+      </c>
+      <c r="L70" s="3" t="n">
+        <v>-0.03302905624960453</v>
+      </c>
+      <c r="M70" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="N70" s="3" t="n">
+        <v>-7.198583722736943</v>
+      </c>
+      <c r="O70" s="4" t="n">
+        <v>0.3526473526473526</v>
+      </c>
+      <c r="P70" s="3" t="n">
+        <v>0.02687795806014426</v>
+      </c>
+      <c r="Q70" s="4" t="n">
+        <v>0.6843156843156843</v>
+      </c>
+      <c r="R70" s="2" t="n">
+        <v>1359</v>
+      </c>
+      <c r="S70" s="4" t="n">
+        <v>0.5294705294705294</v>
+      </c>
+      <c r="T70" s="4" t="n">
+        <v>-0.02589462559755418</v>
+      </c>
+      <c r="U70" s="4" t="n">
+        <v>0.6133866133866134</v>
+      </c>
+      <c r="V70" s="4" t="n">
+        <v>0.01377325668290949</v>
+      </c>
+      <c r="W70" s="4" t="n">
+        <v>0.8561438561438561</v>
+      </c>
+      <c r="X70" s="3" t="n">
+        <v>0.003615661856912408</v>
+      </c>
+      <c r="Y70" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="Z70" s="3" t="n">
+        <v>0.004969700834084101</v>
+      </c>
+      <c r="AA70" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="AB70" s="4" t="n">
+        <v>-0.1609754171500634</v>
+      </c>
+      <c r="AC70" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>rf</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout_changepoint_vix_cash</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="H71" s="4" t="n">
+        <v>0.02462616971307601</v>
+      </c>
+      <c r="I71" s="4" t="n">
+        <v>0.8704633560972825</v>
+      </c>
+      <c r="J71" s="3" t="n">
+        <v>-0.03317545961847196</v>
+      </c>
+      <c r="K71" s="4" t="n">
+        <v>0.2697302697302698</v>
+      </c>
+      <c r="L71" s="3" t="n">
+        <v>-0.08305368209398784</v>
+      </c>
+      <c r="M71" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="N71" s="3" t="n">
+        <v>-11.00529369624163</v>
+      </c>
+      <c r="O71" s="4" t="n">
+        <v>0.4375624375624376</v>
+      </c>
+      <c r="P71" s="3" t="n">
+        <v>0.2233808717795261</v>
+      </c>
+      <c r="Q71" s="4" t="n">
+        <v>0.04095904095904096</v>
+      </c>
+      <c r="R71" s="2" t="n">
+        <v>-1494</v>
+      </c>
+      <c r="S71" s="4" t="n">
+        <v>0.3446553446553446</v>
+      </c>
+      <c r="T71" s="4" t="n">
+        <v>0.04297323878995754</v>
+      </c>
+      <c r="U71" s="4" t="n">
+        <v>0.7242757242757243</v>
+      </c>
+      <c r="V71" s="4" t="n">
+        <v>-0.09999078850150347</v>
+      </c>
+      <c r="W71" s="4" t="n">
+        <v>0.05794205794205794</v>
+      </c>
+      <c r="X71" s="3" t="n">
+        <v>0.009746801491535754</v>
+      </c>
+      <c r="Y71" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="Z71" s="3" t="n">
+        <v>0.01058621889118865</v>
+      </c>
+      <c r="AA71" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="AB71" s="4" t="n">
+        <v>-0.6392609951618802</v>
+      </c>
+      <c r="AC71" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>rf</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>hmm</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>gspc</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout_hmm_gspc_cash</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="H72" s="4" t="n">
+        <v>-0.06940582975805414</v>
+      </c>
+      <c r="I72" s="4" t="n">
+        <v>0.3949426205579897</v>
+      </c>
+      <c r="J72" s="3" t="n">
+        <v>-0.02578421749611479</v>
+      </c>
+      <c r="K72" s="4" t="n">
+        <v>0.2097902097902098</v>
+      </c>
+      <c r="L72" s="3" t="n">
+        <v>-0.02651903924334481</v>
+      </c>
+      <c r="M72" s="4" t="n">
+        <v>0.01698301698301698</v>
+      </c>
+      <c r="N72" s="3" t="n">
+        <v>-9.267579622814765</v>
+      </c>
+      <c r="O72" s="4" t="n">
+        <v>0.3816183816183816</v>
+      </c>
+      <c r="P72" s="3" t="n">
+        <v>0.01314418747081669</v>
+      </c>
+      <c r="Q72" s="4" t="n">
+        <v>0.8201798201798202</v>
+      </c>
+      <c r="R72" s="2" t="n">
+        <v>-927</v>
+      </c>
+      <c r="S72" s="4" t="n">
+        <v>0.6513486513486514</v>
+      </c>
+      <c r="T72" s="4" t="n">
+        <v>-0.04411503890769711</v>
+      </c>
+      <c r="U72" s="4" t="n">
+        <v>0.5624375624375625</v>
+      </c>
+      <c r="V72" s="4" t="n">
+        <v>-0.01898063086699978</v>
+      </c>
+      <c r="W72" s="4" t="n">
+        <v>0.5894105894105894</v>
+      </c>
+      <c r="X72" s="3" t="n">
+        <v>0.001967094894967446</v>
+      </c>
+      <c r="Y72" s="4" t="n">
+        <v>0.03396603396603397</v>
+      </c>
+      <c r="Z72" s="3" t="n">
+        <v>0.003081616254124599</v>
+      </c>
+      <c r="AA72" s="4" t="n">
+        <v>0.04795204795204795</v>
+      </c>
+      <c r="AB72" s="4" t="n">
+        <v>-0.2390340166138877</v>
+      </c>
+      <c r="AC72" s="4" t="n">
+        <v>0.001998001998001998</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>rf</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout_wasserstein_gspc_vix_cash</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="H73" s="4" t="n">
+        <v>-0.1221611700906519</v>
+      </c>
+      <c r="I73" s="4" t="n">
+        <v>0.3457712084327863</v>
+      </c>
+      <c r="J73" s="3" t="n">
+        <v>-0.04714525616271253</v>
+      </c>
+      <c r="K73" s="4" t="n">
+        <v>0.09090909090909091</v>
+      </c>
+      <c r="L73" s="3" t="n">
+        <v>-0.06268868333053623</v>
+      </c>
+      <c r="M73" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="N73" s="3" t="n">
+        <v>-13.52846278457541</v>
+      </c>
+      <c r="O73" s="4" t="n">
+        <v>0.3046953046953047</v>
+      </c>
+      <c r="P73" s="3" t="n">
+        <v>0.05873609596622265</v>
+      </c>
+      <c r="Q73" s="4" t="n">
+        <v>0.5584415584415584</v>
+      </c>
+      <c r="R73" s="2" t="n">
+        <v>-126</v>
+      </c>
+      <c r="S73" s="4" t="n">
+        <v>0.8551448551448552</v>
+      </c>
+      <c r="T73" s="4" t="n">
+        <v>-0.07319527624305919</v>
+      </c>
+      <c r="U73" s="4" t="n">
+        <v>0.4595404595404595</v>
+      </c>
+      <c r="V73" s="4" t="n">
+        <v>-0.008933094529282593</v>
+      </c>
+      <c r="W73" s="4" t="n">
+        <v>0.8561438561438561</v>
+      </c>
+      <c r="X73" s="3" t="n">
+        <v>0.0062359050644326</v>
+      </c>
+      <c r="Y73" s="4" t="n">
+        <v>0.001998001998001998</v>
+      </c>
+      <c r="Z73" s="3" t="n">
+        <v>0.007515481692385185</v>
+      </c>
+      <c r="AA73" s="4" t="n">
+        <v>0.004995004995004995</v>
+      </c>
+      <c r="AB73" s="4" t="n">
+        <v>-0.5159399654547614</v>
+      </c>
+      <c r="AC73" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>rf</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout_changepoint_vix_hrp</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="H74" s="4" t="n">
+        <v>0.0194681338092216</v>
+      </c>
+      <c r="I74" s="4" t="n">
+        <v>0.6845718090633315</v>
+      </c>
+      <c r="J74" s="3" t="n">
+        <v>-0.007123248928485079</v>
+      </c>
+      <c r="K74" s="4" t="n">
+        <v>0.5474525474525475</v>
+      </c>
+      <c r="L74" s="3" t="n">
+        <v>-0.02495663714836441</v>
+      </c>
+      <c r="M74" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="N74" s="3" t="n">
+        <v>-3.168271582359786</v>
+      </c>
+      <c r="O74" s="4" t="n">
+        <v>0.6143856143856143</v>
+      </c>
+      <c r="P74" s="3" t="n">
+        <v>0.06752006803606014</v>
+      </c>
+      <c r="Q74" s="4" t="n">
+        <v>0.08491508491508491</v>
+      </c>
+      <c r="R74" s="2" t="n">
+        <v>-1446</v>
+      </c>
+      <c r="S74" s="4" t="n">
+        <v>0.3176823176823177</v>
+      </c>
+      <c r="T74" s="4" t="n">
+        <v>0.0148697530963596</v>
+      </c>
+      <c r="U74" s="4" t="n">
+        <v>0.6673326673326674</v>
+      </c>
+      <c r="V74" s="4" t="n">
+        <v>-0.03734153591068734</v>
+      </c>
+      <c r="W74" s="4" t="n">
+        <v>0.06493506493506493</v>
+      </c>
+      <c r="X74" s="3" t="n">
+        <v>0.002994309677799498</v>
+      </c>
+      <c r="Y74" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="Z74" s="3" t="n">
+        <v>0.003523920261123411</v>
+      </c>
+      <c r="AA74" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="AB74" s="4" t="n">
+        <v>-0.1305305581765009</v>
+      </c>
+      <c r="AC74" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>rf</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>hmm</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>gspc</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout_hmm_gspc_hrp</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="H75" s="4" t="n">
+        <v>-0.04447597721442159</v>
+      </c>
+      <c r="I75" s="4" t="n">
+        <v>0.1654117436338651</v>
+      </c>
+      <c r="J75" s="3" t="n">
+        <v>-0.01374118725227788</v>
+      </c>
+      <c r="K75" s="4" t="n">
+        <v>0.1328671328671329</v>
+      </c>
+      <c r="L75" s="3" t="n">
+        <v>-0.008551917214756205</v>
+      </c>
+      <c r="M75" s="4" t="n">
+        <v>0.001998001998001998</v>
+      </c>
+      <c r="N75" s="3" t="n">
+        <v>-5.657249800302653</v>
+      </c>
+      <c r="O75" s="4" t="n">
+        <v>0.3136863136863137</v>
+      </c>
+      <c r="P75" s="3" t="n">
+        <v>0.01314418747081669</v>
+      </c>
+      <c r="Q75" s="4" t="n">
+        <v>0.5724275724275725</v>
+      </c>
+      <c r="R75" s="2" t="n">
+        <v>-141</v>
+      </c>
+      <c r="S75" s="4" t="n">
+        <v>0.7262737262737263</v>
+      </c>
+      <c r="T75" s="4" t="n">
+        <v>-0.02105898578385726</v>
+      </c>
+      <c r="U75" s="4" t="n">
+        <v>0.3966033966033966</v>
+      </c>
+      <c r="V75" s="4" t="n">
+        <v>-0.007610873856909339</v>
+      </c>
+      <c r="W75" s="4" t="n">
+        <v>0.4665334665334666</v>
+      </c>
+      <c r="X75" s="3" t="n">
+        <v>0.0007313313234650586</v>
+      </c>
+      <c r="Y75" s="4" t="n">
+        <v>0.02797202797202797</v>
+      </c>
+      <c r="Z75" s="3" t="n">
+        <v>0.001086172914240638</v>
+      </c>
+      <c r="AA75" s="4" t="n">
+        <v>0.008991008991008992</v>
+      </c>
+      <c r="AB75" s="4" t="n">
+        <v>-0.04655675018306205</v>
+      </c>
+      <c r="AC75" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>rf</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout_wasserstein_gspc_vix_hrp</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="H76" s="4" t="n">
+        <v>-0.04693320523734779</v>
+      </c>
+      <c r="I76" s="4" t="n">
+        <v>0.2652766961232654</v>
+      </c>
+      <c r="J76" s="3" t="n">
+        <v>-0.0183581538044484</v>
+      </c>
+      <c r="K76" s="4" t="n">
+        <v>0.08791208791208792</v>
+      </c>
+      <c r="L76" s="3" t="n">
+        <v>-0.01900178561014912</v>
+      </c>
+      <c r="M76" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="N76" s="3" t="n">
+        <v>-7.169345375214647</v>
+      </c>
+      <c r="O76" s="4" t="n">
+        <v>0.3056943056943057</v>
+      </c>
+      <c r="P76" s="3" t="n">
+        <v>0.02013985957772413</v>
+      </c>
+      <c r="Q76" s="4" t="n">
+        <v>0.4935064935064935</v>
+      </c>
+      <c r="R76" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="S76" s="4" t="n">
+        <v>0.8631368631368631</v>
+      </c>
+      <c r="T76" s="4" t="n">
+        <v>-0.02747279064219421</v>
+      </c>
+      <c r="U76" s="4" t="n">
+        <v>0.3986013986013986</v>
+      </c>
+      <c r="V76" s="4" t="n">
+        <v>0.006171883824825058</v>
+      </c>
+      <c r="W76" s="4" t="n">
+        <v>0.8941058941058941</v>
+      </c>
+      <c r="X76" s="3" t="n">
+        <v>0.002079175997510358</v>
+      </c>
+      <c r="Y76" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="Z76" s="3" t="n">
+        <v>0.002817298116207973</v>
+      </c>
+      <c r="AA76" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="AB76" s="4" t="n">
+        <v>-0.1024890325891425</v>
+      </c>
+      <c r="AC76" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>lstm</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank_changepoint_vix_cash</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank</t>
+        </is>
+      </c>
+      <c r="H77" s="4" t="n">
+        <v>-0.1649408751634775</v>
+      </c>
+      <c r="I77" s="4" t="n">
+        <v>0.2720734837569244</v>
+      </c>
+      <c r="J77" s="3" t="n">
+        <v>-0.05837982849719815</v>
+      </c>
+      <c r="K77" s="4" t="n">
+        <v>0.06493506493506493</v>
+      </c>
+      <c r="L77" s="3" t="n">
+        <v>-0.08964305827678912</v>
+      </c>
+      <c r="M77" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="N77" s="3" t="n">
+        <v>-13.22018821254692</v>
+      </c>
+      <c r="O77" s="4" t="n">
+        <v>0.3136863136863137</v>
+      </c>
+      <c r="P77" s="3" t="n">
+        <v>0.1426497617656427</v>
+      </c>
+      <c r="Q77" s="4" t="n">
+        <v>0.2727272727272727</v>
+      </c>
+      <c r="R77" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="S77" s="4" t="n">
+        <v>0.985014985014985</v>
+      </c>
+      <c r="T77" s="4" t="n">
+        <v>-0.07127918028777966</v>
+      </c>
+      <c r="U77" s="4" t="n">
+        <v>0.5374625374625375</v>
+      </c>
+      <c r="V77" s="4" t="n">
+        <v>-0.03335478150236226</v>
+      </c>
+      <c r="W77" s="4" t="n">
+        <v>0.6063936063936064</v>
+      </c>
+      <c r="X77" s="3" t="n">
+        <v>0.009627547355853375</v>
+      </c>
+      <c r="Y77" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="Z77" s="3" t="n">
+        <v>0.01183729594430986</v>
+      </c>
+      <c r="AA77" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="AB77" s="4" t="n">
+        <v>-0.6423902673887862</v>
+      </c>
+      <c r="AC77" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>lstm</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>hmm</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>gspc</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank_hmm_gspc_cash</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank</t>
+        </is>
+      </c>
+      <c r="H78" s="4" t="n">
+        <v>-0.04504531036964063</v>
+      </c>
+      <c r="I78" s="4" t="n">
+        <v>0.7326437504341263</v>
+      </c>
+      <c r="J78" s="3" t="n">
+        <v>-0.03449074785336552</v>
+      </c>
+      <c r="K78" s="4" t="n">
+        <v>0.1528471528471528</v>
+      </c>
+      <c r="L78" s="3" t="n">
+        <v>-0.06763238925070927</v>
+      </c>
+      <c r="M78" s="4" t="n">
+        <v>0.002997002997002997</v>
+      </c>
+      <c r="N78" s="3" t="n">
+        <v>-9.951617543731789</v>
+      </c>
+      <c r="O78" s="4" t="n">
+        <v>0.3636363636363636</v>
+      </c>
+      <c r="P78" s="3" t="n">
+        <v>0.06891331939562173</v>
+      </c>
+      <c r="Q78" s="4" t="n">
+        <v>0.5684315684315684</v>
+      </c>
+      <c r="R78" s="2" t="n">
+        <v>1718</v>
+      </c>
+      <c r="S78" s="4" t="n">
+        <v>0.3726273726273726</v>
+      </c>
+      <c r="T78" s="4" t="n">
+        <v>-0.04130347373278354</v>
+      </c>
+      <c r="U78" s="4" t="n">
+        <v>0.6353646353646354</v>
+      </c>
+      <c r="V78" s="4" t="n">
+        <v>0.05166610809153432</v>
+      </c>
+      <c r="W78" s="4" t="n">
+        <v>0.6183816183816184</v>
+      </c>
+      <c r="X78" s="3" t="n">
+        <v>0.005662092828885575</v>
+      </c>
+      <c r="Y78" s="4" t="n">
+        <v>0.001998001998001998</v>
+      </c>
+      <c r="Z78" s="3" t="n">
+        <v>0.008976057330007683</v>
+      </c>
+      <c r="AA78" s="4" t="n">
+        <v>0.006993006993006993</v>
+      </c>
+      <c r="AB78" s="4" t="n">
+        <v>-0.5145410036612611</v>
+      </c>
+      <c r="AC78" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>lstm</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank_wasserstein_gspc_vix_cash</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank</t>
+        </is>
+      </c>
+      <c r="H79" s="4" t="n">
+        <v>-0.001257580709381543</v>
+      </c>
+      <c r="I79" s="4" t="n">
+        <v>0.9939123049093925</v>
+      </c>
+      <c r="J79" s="3" t="n">
+        <v>-0.04198937805358044</v>
+      </c>
+      <c r="K79" s="4" t="n">
+        <v>0.1288711288711289</v>
+      </c>
+      <c r="L79" s="3" t="n">
+        <v>-0.1047907365213937</v>
+      </c>
+      <c r="M79" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="N79" s="3" t="n">
+        <v>-11.19749023766148</v>
+      </c>
+      <c r="O79" s="4" t="n">
+        <v>0.3686313686313686</v>
+      </c>
+      <c r="P79" s="3" t="n">
+        <v>0.3483636476420208</v>
+      </c>
+      <c r="Q79" s="4" t="n">
+        <v>0.02597402597402598</v>
+      </c>
+      <c r="R79" s="2" t="n">
+        <v>-207</v>
+      </c>
+      <c r="S79" s="4" t="n">
+        <v>0.7942057942057942</v>
+      </c>
+      <c r="T79" s="4" t="n">
+        <v>0.0691562012100527</v>
+      </c>
+      <c r="U79" s="4" t="n">
+        <v>0.5774225774225774</v>
+      </c>
+      <c r="V79" s="4" t="n">
+        <v>-0.07493556416861707</v>
+      </c>
+      <c r="W79" s="4" t="n">
+        <v>0.1898101898101898</v>
+      </c>
+      <c r="X79" s="3" t="n">
+        <v>0.009485951622722475</v>
+      </c>
+      <c r="Y79" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="Z79" s="3" t="n">
+        <v>0.0140182793270056</v>
+      </c>
+      <c r="AA79" s="4" t="n">
+        <v>0.001998001998001998</v>
+      </c>
+      <c r="AB79" s="4" t="n">
+        <v>-0.7351070911405292</v>
+      </c>
+      <c r="AC79" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>lstm</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank_changepoint_vix_hrp</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank</t>
+        </is>
+      </c>
+      <c r="H80" s="4" t="n">
+        <v>0.02720222004946002</v>
+      </c>
+      <c r="I80" s="4" t="n">
+        <v>0.5986815480265986</v>
+      </c>
+      <c r="J80" s="3" t="n">
+        <v>-0.008008855126191455</v>
+      </c>
+      <c r="K80" s="4" t="n">
+        <v>0.5314685314685315</v>
+      </c>
+      <c r="L80" s="3" t="n">
+        <v>-0.03343117223426945</v>
+      </c>
+      <c r="M80" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="N80" s="3" t="n">
+        <v>-3.113259336852437</v>
+      </c>
+      <c r="O80" s="4" t="n">
+        <v>0.6163836163836164</v>
+      </c>
+      <c r="P80" s="3" t="n">
+        <v>0.1588645129071439</v>
+      </c>
+      <c r="Q80" s="4" t="n">
+        <v>0.04295704295704296</v>
+      </c>
+      <c r="R80" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="S80" s="4" t="n">
+        <v>0.8991008991008991</v>
+      </c>
+      <c r="T80" s="4" t="n">
+        <v>0.04286538349408234</v>
+      </c>
+      <c r="U80" s="4" t="n">
+        <v>0.3646353646353646</v>
+      </c>
+      <c r="V80" s="4" t="n">
+        <v>-0.05012634921190749</v>
+      </c>
+      <c r="W80" s="4" t="n">
+        <v>0.08291708291708291</v>
+      </c>
+      <c r="X80" s="3" t="n">
+        <v>0.003257111823345597</v>
+      </c>
+      <c r="Y80" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="Z80" s="3" t="n">
+        <v>0.004995631304451933</v>
+      </c>
+      <c r="AA80" s="4" t="n">
+        <v>0.001998001998001998</v>
+      </c>
+      <c r="AB80" s="4" t="n">
+        <v>-0.1579318884803911</v>
+      </c>
+      <c r="AC80" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>lstm</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>hmm</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>gspc</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank_hmm_gspc_hrp</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank</t>
+        </is>
+      </c>
+      <c r="H81" s="4" t="n">
+        <v>0.03196951581105358</v>
+      </c>
+      <c r="I81" s="4" t="n">
+        <v>0.4594647344401472</v>
+      </c>
+      <c r="J81" s="3" t="n">
+        <v>-0.003870020520917242</v>
+      </c>
+      <c r="K81" s="4" t="n">
+        <v>0.6913086913086913</v>
+      </c>
+      <c r="L81" s="3" t="n">
+        <v>-0.02622682349373737</v>
+      </c>
+      <c r="M81" s="4" t="n">
+        <v>0.002997002997002997</v>
+      </c>
+      <c r="N81" s="3" t="n">
+        <v>-1.580478760581586</v>
+      </c>
+      <c r="O81" s="4" t="n">
+        <v>0.7152847152847153</v>
+      </c>
+      <c r="P81" s="3" t="n">
+        <v>0.1038017176676735</v>
+      </c>
+      <c r="Q81" s="4" t="n">
+        <v>0.06893106893106893</v>
+      </c>
+      <c r="R81" s="2" t="n">
+        <v>144</v>
+      </c>
+      <c r="S81" s="4" t="n">
+        <v>0.7482517482517482</v>
+      </c>
+      <c r="T81" s="4" t="n">
+        <v>0.02765724888994342</v>
+      </c>
+      <c r="U81" s="4" t="n">
+        <v>0.4865134865134865</v>
+      </c>
+      <c r="V81" s="4" t="n">
+        <v>-0.00861667343650338</v>
+      </c>
+      <c r="W81" s="4" t="n">
+        <v>0.6643356643356644</v>
+      </c>
+      <c r="X81" s="3" t="n">
+        <v>0.001795372150376173</v>
+      </c>
+      <c r="Y81" s="4" t="n">
+        <v>0.003996003996003996</v>
+      </c>
+      <c r="Z81" s="3" t="n">
+        <v>0.004113016669084233</v>
+      </c>
+      <c r="AA81" s="4" t="n">
+        <v>0.006993006993006993</v>
+      </c>
+      <c r="AB81" s="4" t="n">
+        <v>-0.1237925179522064</v>
+      </c>
+      <c r="AC81" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>lstm</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank_wasserstein_gspc_vix_hrp</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank</t>
+        </is>
+      </c>
+      <c r="H82" s="4" t="n">
+        <v>0.05062112777665276</v>
+      </c>
+      <c r="I82" s="4" t="n">
+        <v>0.3103746313967121</v>
+      </c>
+      <c r="J82" s="3" t="n">
+        <v>-0.003830387375373168</v>
+      </c>
+      <c r="K82" s="4" t="n">
+        <v>0.6993006993006993</v>
+      </c>
+      <c r="L82" s="3" t="n">
+        <v>-0.03470879993487108</v>
+      </c>
+      <c r="M82" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="N82" s="3" t="n">
+        <v>-1.565037849612926</v>
+      </c>
+      <c r="O82" s="4" t="n">
+        <v>0.7162837162837162</v>
+      </c>
+      <c r="P82" s="3" t="n">
+        <v>0.1108081140441053</v>
+      </c>
+      <c r="Q82" s="4" t="n">
+        <v>0.02697302697302697</v>
+      </c>
+      <c r="R82" s="2" t="n">
+        <v>213</v>
+      </c>
+      <c r="S82" s="4" t="n">
+        <v>0.7892107892107892</v>
+      </c>
+      <c r="T82" s="4" t="n">
+        <v>0.03053170510984365</v>
+      </c>
+      <c r="U82" s="4" t="n">
+        <v>0.4215784215784216</v>
+      </c>
+      <c r="V82" s="4" t="n">
+        <v>-0.03543390332058602</v>
+      </c>
+      <c r="W82" s="4" t="n">
+        <v>0.1338661338661339</v>
+      </c>
+      <c r="X82" s="3" t="n">
+        <v>0.003003046278970564</v>
+      </c>
+      <c r="Y82" s="4" t="n">
+        <v>0.001998001998001998</v>
+      </c>
+      <c r="Z82" s="3" t="n">
+        <v>0.005517413006416196</v>
+      </c>
+      <c r="AA82" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="AB82" s="4" t="n">
+        <v>-0.1676045498560752</v>
+      </c>
+      <c r="AC82" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>lstm</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank_changepoint_vix_cash</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank</t>
+        </is>
+      </c>
+      <c r="H83" s="4" t="n">
+        <v>-0.3004363423359421</v>
+      </c>
+      <c r="I83" s="4" t="n">
+        <v>0.03351727933933436</v>
+      </c>
+      <c r="J83" s="3" t="n">
+        <v>-0.07721196074913601</v>
+      </c>
+      <c r="K83" s="4" t="n">
+        <v>0.01298701298701299</v>
+      </c>
+      <c r="L83" s="3" t="n">
+        <v>-0.0806055207268892</v>
+      </c>
+      <c r="M83" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="N83" s="3" t="n">
+        <v>-16.90491846919132</v>
+      </c>
+      <c r="O83" s="4" t="n">
+        <v>0.2647352647352647</v>
+      </c>
+      <c r="P83" s="3" t="n">
+        <v>0.0593021371853415</v>
+      </c>
+      <c r="Q83" s="4" t="n">
+        <v>0.6023976023976024</v>
+      </c>
+      <c r="R83" s="2" t="n">
+        <v>-51</v>
+      </c>
+      <c r="S83" s="4" t="n">
+        <v>0.9760239760239761</v>
+      </c>
+      <c r="T83" s="4" t="n">
+        <v>-0.137005966246703</v>
+      </c>
+      <c r="U83" s="4" t="n">
+        <v>0.2267732267732268</v>
+      </c>
+      <c r="V83" s="4" t="n">
+        <v>0.01760602504594042</v>
+      </c>
+      <c r="W83" s="4" t="n">
+        <v>0.7702297702297702</v>
+      </c>
+      <c r="X83" s="3" t="n">
+        <v>0.008673966743765882</v>
+      </c>
+      <c r="Y83" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="Z83" s="3" t="n">
+        <v>0.009807972011472873</v>
+      </c>
+      <c r="AA83" s="4" t="n">
+        <v>0.003996003996003996</v>
+      </c>
+      <c r="AB83" s="4" t="n">
+        <v>-0.5981481244703385</v>
+      </c>
+      <c r="AC83" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>lstm</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>hmm</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>gspc</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank_hmm_gspc_cash</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank</t>
+        </is>
+      </c>
+      <c r="H84" s="4" t="n">
+        <v>-0.1112480820248136</v>
+      </c>
+      <c r="I84" s="4" t="n">
+        <v>0.2928935256458355</v>
+      </c>
+      <c r="J84" s="3" t="n">
+        <v>-0.04096959075954455</v>
+      </c>
+      <c r="K84" s="4" t="n">
+        <v>0.07292707292707293</v>
+      </c>
+      <c r="L84" s="3" t="n">
+        <v>-0.04785704558807713</v>
+      </c>
+      <c r="M84" s="4" t="n">
+        <v>0.004995004995004995</v>
+      </c>
+      <c r="N84" s="3" t="n">
+        <v>-12.68023355057283</v>
+      </c>
+      <c r="O84" s="4" t="n">
+        <v>0.2947052947052947</v>
+      </c>
+      <c r="P84" s="3" t="n">
+        <v>-0.01507468424524072</v>
+      </c>
+      <c r="Q84" s="4" t="n">
+        <v>0.8971028971028971</v>
+      </c>
+      <c r="R84" s="2" t="n">
+        <v>1202</v>
+      </c>
+      <c r="S84" s="4" t="n">
+        <v>0.3386613386613387</v>
+      </c>
+      <c r="T84" s="4" t="n">
+        <v>-0.08077810427510199</v>
+      </c>
+      <c r="U84" s="4" t="n">
+        <v>0.3836163836163836</v>
+      </c>
+      <c r="V84" s="4" t="n">
+        <v>0.06033225355674399</v>
+      </c>
+      <c r="W84" s="4" t="n">
+        <v>0.4745254745254745</v>
+      </c>
+      <c r="X84" s="3" t="n">
+        <v>0.003858759563421105</v>
+      </c>
+      <c r="Y84" s="4" t="n">
+        <v>0.004995004995004995</v>
+      </c>
+      <c r="Z84" s="3" t="n">
+        <v>0.005947535498035814</v>
+      </c>
+      <c r="AA84" s="4" t="n">
+        <v>0.01398601398601399</v>
+      </c>
+      <c r="AB84" s="4" t="n">
+        <v>-0.3797315677574212</v>
+      </c>
+      <c r="AC84" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>lstm</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank_wasserstein_gspc_vix_cash</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank</t>
+        </is>
+      </c>
+      <c r="H85" s="4" t="n">
+        <v>-0.2209029157948325</v>
+      </c>
+      <c r="I85" s="4" t="n">
+        <v>0.1316523379251462</v>
+      </c>
+      <c r="J85" s="3" t="n">
+        <v>-0.06727767234676874</v>
+      </c>
+      <c r="K85" s="4" t="n">
+        <v>0.01698301698301698</v>
+      </c>
+      <c r="L85" s="3" t="n">
+        <v>-0.08561247002761121</v>
+      </c>
+      <c r="M85" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="N85" s="3" t="n">
+        <v>-16.10522357940627</v>
+      </c>
+      <c r="O85" s="4" t="n">
+        <v>0.2697302697302698</v>
+      </c>
+      <c r="P85" s="3" t="n">
+        <v>0.2084357088009259</v>
+      </c>
+      <c r="Q85" s="4" t="n">
+        <v>0.1678321678321678</v>
+      </c>
+      <c r="R85" s="2" t="n">
+        <v>151</v>
+      </c>
+      <c r="S85" s="4" t="n">
+        <v>0.8461538461538461</v>
+      </c>
+      <c r="T85" s="4" t="n">
+        <v>-0.07206203164202232</v>
+      </c>
+      <c r="U85" s="4" t="n">
+        <v>0.5304695304695305</v>
+      </c>
+      <c r="V85" s="4" t="n">
+        <v>-3.318892835169063e-06</v>
+      </c>
+      <c r="W85" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="X85" s="3" t="n">
+        <v>0.008187077860104832</v>
+      </c>
+      <c r="Y85" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="Z85" s="3" t="n">
+        <v>0.01082936712193612</v>
+      </c>
+      <c r="AA85" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="AB85" s="4" t="n">
+        <v>-0.6305888325192094</v>
+      </c>
+      <c r="AC85" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>lstm</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank_changepoint_vix_hrp</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank</t>
+        </is>
+      </c>
+      <c r="H86" s="4" t="n">
+        <v>-0.02867310323589712</v>
+      </c>
+      <c r="I86" s="4" t="n">
+        <v>0.5458148954809834</v>
+      </c>
+      <c r="J86" s="3" t="n">
+        <v>-0.01756330364960951</v>
+      </c>
+      <c r="K86" s="4" t="n">
+        <v>0.1398601398601399</v>
+      </c>
+      <c r="L86" s="3" t="n">
+        <v>-0.02632149093158812</v>
+      </c>
+      <c r="M86" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="N86" s="3" t="n">
+        <v>-7.008211258090473</v>
+      </c>
+      <c r="O86" s="4" t="n">
+        <v>0.3496503496503496</v>
+      </c>
+      <c r="P86" s="3" t="n">
+        <v>0.08751977085293483</v>
+      </c>
+      <c r="Q86" s="4" t="n">
+        <v>0.09490509490509491</v>
+      </c>
+      <c r="R86" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="S86" s="4" t="n">
+        <v>0.7702297702297702</v>
+      </c>
+      <c r="T86" s="4" t="n">
+        <v>0.002050577583933816</v>
+      </c>
+      <c r="U86" s="4" t="n">
+        <v>0.948051948051948</v>
+      </c>
+      <c r="V86" s="4" t="n">
+        <v>-0.01049341906134352</v>
+      </c>
+      <c r="W86" s="4" t="n">
+        <v>0.4675324675324675</v>
+      </c>
+      <c r="X86" s="3" t="n">
+        <v>0.002667449211006076</v>
+      </c>
+      <c r="Y86" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="Z86" s="3" t="n">
+        <v>0.003658683301156762</v>
+      </c>
+      <c r="AA86" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="AB86" s="4" t="n">
+        <v>-0.1264729242346645</v>
+      </c>
+      <c r="AC86" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>lstm</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>hmm</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>gspc</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank_hmm_gspc_hrp</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank</t>
+        </is>
+      </c>
+      <c r="H87" s="4" t="n">
+        <v>-0.001536903290862149</v>
+      </c>
+      <c r="I87" s="4" t="n">
+        <v>0.9688210519269079</v>
+      </c>
+      <c r="J87" s="3" t="n">
+        <v>-0.008729527073628965</v>
+      </c>
+      <c r="K87" s="4" t="n">
+        <v>0.3146853146853147</v>
+      </c>
+      <c r="L87" s="3" t="n">
+        <v>-0.01884612508618658</v>
+      </c>
+      <c r="M87" s="4" t="n">
+        <v>0.001998001998001998</v>
+      </c>
+      <c r="N87" s="3" t="n">
+        <v>-3.857677067333821</v>
+      </c>
+      <c r="O87" s="4" t="n">
+        <v>0.4505494505494506</v>
+      </c>
+      <c r="P87" s="3" t="n">
+        <v>0.05305208260371663</v>
+      </c>
+      <c r="Q87" s="4" t="n">
+        <v>0.1828171828171828</v>
+      </c>
+      <c r="R87" s="2" t="n">
+        <v>240</v>
+      </c>
+      <c r="S87" s="4" t="n">
+        <v>0.6383616383616384</v>
+      </c>
+      <c r="T87" s="4" t="n">
+        <v>0.005159851437725793</v>
+      </c>
+      <c r="U87" s="4" t="n">
+        <v>0.8661338661338661</v>
+      </c>
+      <c r="V87" s="4" t="n">
+        <v>0.01167381095806339</v>
+      </c>
+      <c r="W87" s="4" t="n">
+        <v>0.8511488511488512</v>
+      </c>
+      <c r="X87" s="3" t="n">
+        <v>0.001661757860106767</v>
+      </c>
+      <c r="Y87" s="4" t="n">
+        <v>0.003996003996003996</v>
+      </c>
+      <c r="Z87" s="3" t="n">
+        <v>0.002828485363474745</v>
+      </c>
+      <c r="AA87" s="4" t="n">
+        <v>0.007992007992007992</v>
+      </c>
+      <c r="AB87" s="4" t="n">
+        <v>-0.08976848875853105</v>
+      </c>
+      <c r="AC87" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>lstm</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank_wasserstein_gspc_vix_hrp</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank</t>
+        </is>
+      </c>
+      <c r="H88" s="4" t="n">
+        <v>-0.01424701384538298</v>
+      </c>
+      <c r="I88" s="4" t="n">
+        <v>0.764843165732682</v>
+      </c>
+      <c r="J88" s="3" t="n">
+        <v>-0.01521465218802559</v>
+      </c>
+      <c r="K88" s="4" t="n">
+        <v>0.1708291708291708</v>
+      </c>
+      <c r="L88" s="3" t="n">
+        <v>-0.02770564920129498</v>
+      </c>
+      <c r="M88" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="N88" s="3" t="n">
+        <v>-6.236024928630483</v>
+      </c>
+      <c r="O88" s="4" t="n">
+        <v>0.3636363636363636</v>
+      </c>
+      <c r="P88" s="3" t="n">
+        <v>0.07208253015547172</v>
+      </c>
+      <c r="Q88" s="4" t="n">
+        <v>0.1548451548451548</v>
+      </c>
+      <c r="R88" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="S88" s="4" t="n">
+        <v>0.8851148851148851</v>
+      </c>
+      <c r="T88" s="4" t="n">
+        <v>1.246462135146009e-06</v>
+      </c>
+      <c r="U88" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="V88" s="4" t="n">
+        <v>-0.0004203280548094601</v>
+      </c>
+      <c r="W88" s="4" t="n">
+        <v>0.997002997002997</v>
+      </c>
+      <c r="X88" s="3" t="n">
+        <v>0.00274858499524722</v>
+      </c>
+      <c r="Y88" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="Z88" s="3" t="n">
+        <v>0.004149592042738719</v>
+      </c>
+      <c r="AA88" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="AB88" s="4" t="n">
+        <v>-0.1344805248587563</v>
+      </c>
+      <c r="AC88" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>lstm</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank_changepoint_vix_cash</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank</t>
+        </is>
+      </c>
+      <c r="H89" s="4" t="n">
+        <v>0.008914889867638708</v>
+      </c>
+      <c r="I89" s="4" t="n">
+        <v>0.9522592251634263</v>
+      </c>
+      <c r="J89" s="3" t="n">
+        <v>-0.03614581081185342</v>
+      </c>
+      <c r="K89" s="4" t="n">
+        <v>0.2047952047952048</v>
+      </c>
+      <c r="L89" s="3" t="n">
+        <v>-0.07834741562303371</v>
+      </c>
+      <c r="M89" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="N89" s="3" t="n">
+        <v>-12.59204217842065</v>
+      </c>
+      <c r="O89" s="4" t="n">
+        <v>0.3936063936063936</v>
+      </c>
+      <c r="P89" s="3" t="n">
+        <v>0.1856876422906277</v>
+      </c>
+      <c r="Q89" s="4" t="n">
+        <v>0.04095904095904096</v>
+      </c>
+      <c r="R89" s="2" t="n">
+        <v>-209</v>
+      </c>
+      <c r="S89" s="4" t="n">
+        <v>0.6643356643356644</v>
+      </c>
+      <c r="T89" s="4" t="n">
+        <v>0.02527354662150366</v>
+      </c>
+      <c r="U89" s="4" t="n">
+        <v>0.8341658341658341</v>
+      </c>
+      <c r="V89" s="4" t="n">
+        <v>-0.08432872443632954</v>
+      </c>
+      <c r="W89" s="4" t="n">
+        <v>0.06293706293706294</v>
+      </c>
+      <c r="X89" s="3" t="n">
+        <v>0.009457534278688822</v>
+      </c>
+      <c r="Y89" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="Z89" s="3" t="n">
+        <v>0.01002179906943215</v>
+      </c>
+      <c r="AA89" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="AB89" s="4" t="n">
+        <v>-0.609501820501047</v>
+      </c>
+      <c r="AC89" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>lstm</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>hmm</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>gspc</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank_hmm_gspc_cash</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank</t>
+        </is>
+      </c>
+      <c r="H90" s="4" t="n">
+        <v>-0.06970566991216529</v>
+      </c>
+      <c r="I90" s="4" t="n">
+        <v>0.3815167664070725</v>
+      </c>
+      <c r="J90" s="3" t="n">
+        <v>-0.02550692442064174</v>
+      </c>
+      <c r="K90" s="4" t="n">
+        <v>0.1708291708291708</v>
+      </c>
+      <c r="L90" s="3" t="n">
+        <v>-0.02482487890034202</v>
+      </c>
+      <c r="M90" s="4" t="n">
+        <v>0.01798201798201798</v>
+      </c>
+      <c r="N90" s="3" t="n">
+        <v>-9.963799795037096</v>
+      </c>
+      <c r="O90" s="4" t="n">
+        <v>0.3516483516483517</v>
+      </c>
+      <c r="P90" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q90" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="R90" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S90" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="T90" s="4" t="n">
+        <v>-0.0523095478075872</v>
+      </c>
+      <c r="U90" s="4" t="n">
+        <v>0.4855144855144855</v>
+      </c>
+      <c r="V90" s="4" t="n">
+        <v>-0.00637398497550834</v>
+      </c>
+      <c r="W90" s="4" t="n">
+        <v>0.7922077922077922</v>
+      </c>
+      <c r="X90" s="3" t="n">
+        <v>0.002034988304881989</v>
+      </c>
+      <c r="Y90" s="4" t="n">
+        <v>0.01398601398601399</v>
+      </c>
+      <c r="Z90" s="3" t="n">
+        <v>0.002830658658355072</v>
+      </c>
+      <c r="AA90" s="4" t="n">
+        <v>0.05494505494505494</v>
+      </c>
+      <c r="AB90" s="4" t="n">
+        <v>-0.2255411889395879</v>
+      </c>
+      <c r="AC90" s="4" t="n">
+        <v>0.001998001998001998</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>lstm</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank_wasserstein_gspc_vix_cash</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank</t>
+        </is>
+      </c>
+      <c r="H91" s="4" t="n">
+        <v>-0.1063449771959567</v>
+      </c>
+      <c r="I91" s="4" t="n">
+        <v>0.4100938900576007</v>
+      </c>
+      <c r="J91" s="3" t="n">
+        <v>-0.04506517407888178</v>
+      </c>
+      <c r="K91" s="4" t="n">
+        <v>0.08391608391608392</v>
+      </c>
+      <c r="L91" s="3" t="n">
+        <v>-0.06022297837236498</v>
+      </c>
+      <c r="M91" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="N91" s="3" t="n">
+        <v>-14.3167873936772</v>
+      </c>
+      <c r="O91" s="4" t="n">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="P91" s="3" t="n">
+        <v>0.05607051061599111</v>
+      </c>
+      <c r="Q91" s="4" t="n">
+        <v>0.5264735264735265</v>
+      </c>
+      <c r="R91" s="2" t="n">
+        <v>861</v>
+      </c>
+      <c r="S91" s="4" t="n">
+        <v>0.4965034965034965</v>
+      </c>
+      <c r="T91" s="4" t="n">
+        <v>-0.07379615922477464</v>
+      </c>
+      <c r="U91" s="4" t="n">
+        <v>0.4805194805194805</v>
+      </c>
+      <c r="V91" s="4" t="n">
+        <v>-0.01510746220836562</v>
+      </c>
+      <c r="W91" s="4" t="n">
+        <v>0.7122877122877123</v>
+      </c>
+      <c r="X91" s="3" t="n">
+        <v>0.00620398204985626</v>
+      </c>
+      <c r="Y91" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="Z91" s="3" t="n">
+        <v>0.007224449626679032</v>
+      </c>
+      <c r="AA91" s="4" t="n">
+        <v>0.005994005994005994</v>
+      </c>
+      <c r="AB91" s="4" t="n">
+        <v>-0.4949373761536499</v>
+      </c>
+      <c r="AC91" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>lstm</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank_changepoint_vix_hrp</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank</t>
+        </is>
+      </c>
+      <c r="H92" s="4" t="n">
+        <v>-0.004656591842314043</v>
+      </c>
+      <c r="I92" s="4" t="n">
+        <v>0.9152235527833803</v>
+      </c>
+      <c r="J92" s="3" t="n">
+        <v>-0.01009268558871736</v>
+      </c>
+      <c r="K92" s="4" t="n">
+        <v>0.3206793206793207</v>
+      </c>
+      <c r="L92" s="3" t="n">
+        <v>-0.01896048477662829</v>
+      </c>
+      <c r="M92" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="N92" s="3" t="n">
+        <v>-4.694722077135506</v>
+      </c>
+      <c r="O92" s="4" t="n">
+        <v>0.4605394605394605</v>
+      </c>
+      <c r="P92" s="3" t="n">
+        <v>0.01602696311713037</v>
+      </c>
+      <c r="Q92" s="4" t="n">
+        <v>0.6193806193806194</v>
+      </c>
+      <c r="R92" s="2" t="n">
+        <v>-96</v>
+      </c>
+      <c r="S92" s="4" t="n">
+        <v>0.6393606393606394</v>
+      </c>
+      <c r="T92" s="4" t="n">
+        <v>-0.01338936689497808</v>
+      </c>
+      <c r="U92" s="4" t="n">
+        <v>0.7152847152847153</v>
+      </c>
+      <c r="V92" s="4" t="n">
+        <v>-0.01578626201050459</v>
+      </c>
+      <c r="W92" s="4" t="n">
+        <v>0.2447552447552448</v>
+      </c>
+      <c r="X92" s="3" t="n">
+        <v>0.002336064139136253</v>
+      </c>
+      <c r="Y92" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="Z92" s="3" t="n">
+        <v>0.002668282031530345</v>
+      </c>
+      <c r="AA92" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="AB92" s="4" t="n">
+        <v>-0.1007692363506423</v>
+      </c>
+      <c r="AC92" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>lstm</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>hmm</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>gspc</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank_hmm_gspc_hrp</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank</t>
+        </is>
+      </c>
+      <c r="H93" s="4" t="n">
+        <v>-0.0480440362844898</v>
+      </c>
+      <c r="I93" s="4" t="n">
+        <v>0.09767237904154016</v>
+      </c>
+      <c r="J93" s="3" t="n">
+        <v>-0.01341763096567361</v>
+      </c>
+      <c r="K93" s="4" t="n">
+        <v>0.08391608391608392</v>
+      </c>
+      <c r="L93" s="3" t="n">
+        <v>-0.006210005316750616</v>
+      </c>
+      <c r="M93" s="4" t="n">
+        <v>0.002997002997002997</v>
+      </c>
+      <c r="N93" s="3" t="n">
+        <v>-6.00544626010792</v>
+      </c>
+      <c r="O93" s="4" t="n">
+        <v>0.2617382617382618</v>
+      </c>
+      <c r="P93" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="R93" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S93" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="T93" s="4" t="n">
+        <v>-0.02751684981257366</v>
+      </c>
+      <c r="U93" s="4" t="n">
+        <v>0.2317682317682318</v>
+      </c>
+      <c r="V93" s="4" t="n">
+        <v>0.001807878650440964</v>
+      </c>
+      <c r="W93" s="4" t="n">
+        <v>0.7472527472527473</v>
+      </c>
+      <c r="X93" s="3" t="n">
+        <v>0.0006830660068159883</v>
+      </c>
+      <c r="Y93" s="4" t="n">
+        <v>0.008991008991008992</v>
+      </c>
+      <c r="Z93" s="3" t="n">
+        <v>0.0007096029035354966</v>
+      </c>
+      <c r="AA93" s="4" t="n">
+        <v>0.01198801198801199</v>
+      </c>
+      <c r="AB93" s="4" t="n">
+        <v>-0.03306261122374154</v>
+      </c>
+      <c r="AC93" s="4" t="n">
+        <v>0.002997002997002997</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>lstm</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank_wasserstein_gspc_vix_hrp</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank</t>
+        </is>
+      </c>
+      <c r="H94" s="4" t="n">
+        <v>-0.04289246820548845</v>
+      </c>
+      <c r="I94" s="4" t="n">
+        <v>0.280042036640188</v>
+      </c>
+      <c r="J94" s="3" t="n">
+        <v>-0.01612389573352344</v>
+      </c>
+      <c r="K94" s="4" t="n">
+        <v>0.1018981018981019</v>
+      </c>
+      <c r="L94" s="3" t="n">
+        <v>-0.01506313912427357</v>
+      </c>
+      <c r="M94" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="N94" s="3" t="n">
+        <v>-6.996341999970744</v>
+      </c>
+      <c r="O94" s="4" t="n">
+        <v>0.3136863136863137</v>
+      </c>
+      <c r="P94" s="3" t="n">
+        <v>0.01602696311713037</v>
+      </c>
+      <c r="Q94" s="4" t="n">
+        <v>0.5814185814185814</v>
+      </c>
+      <c r="R94" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="S94" s="4" t="n">
+        <v>0.9140859140859141</v>
+      </c>
+      <c r="T94" s="4" t="n">
+        <v>-0.0261785146892467</v>
+      </c>
+      <c r="U94" s="4" t="n">
+        <v>0.4315684315684316</v>
+      </c>
+      <c r="V94" s="4" t="n">
+        <v>0.00162424250536003</v>
+      </c>
+      <c r="W94" s="4" t="n">
+        <v>0.919080919080919</v>
+      </c>
+      <c r="X94" s="3" t="n">
+        <v>0.001901084788297328</v>
+      </c>
+      <c r="Y94" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="Z94" s="3" t="n">
+        <v>0.00223820427111281</v>
+      </c>
+      <c r="AA94" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="AB94" s="4" t="n">
+        <v>-0.08148216625107696</v>
+      </c>
+      <c r="AC94" s="4" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:V118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -20321,7 +30081,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -29609,7 +39369,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -38897,7 +48657,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -48185,7 +57945,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -57473,7 +67233,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -66691,7 +76451,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
